--- a/code/modules/tests/python_regional_new_tort_metrics_merged.xlsx
+++ b/code/modules/tests/python_regional_new_tort_metrics_merged.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/22756463_student_uwa_edu_au/Documents/M4 Backup/dev/octava/code/modules/tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_54D5686D95899B7CDB193D11595ED87656CC5A09" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1A440BA-3890-0047-944D-492FECE828C7}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_54D5686D9559133BDB982411595ED87656CC5A09" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{798A1D31-69D1-1D4D-8EEF-5E132D5980AA}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="regional_new_tort_merged" sheetId="1" r:id="rId1"/>
@@ -644,35 +644,23 @@
     <t>/Users/milameteor/Library/CloudStorage/OneDrive-UWA/M4 Backup/dev/octava/source/5002/regional_tort_validation/5002_Square_grid_R09_Inferonasal_tort_validation.mat</t>
   </si>
   <si>
-    <t>RMSE_pwaoc_mean</t>
-  </si>
-  <si>
-    <t>RMSE_pwaoc_std</t>
-  </si>
-  <si>
-    <t>RMSE_soam_mean</t>
-  </si>
-  <si>
-    <t>RMSE_soam_std</t>
+    <t>RMSE pwaoc mean</t>
+  </si>
+  <si>
+    <t>RMSE pwaoc std</t>
+  </si>
+  <si>
+    <t>RMSE soam mean</t>
+  </si>
+  <si>
+    <t>RMSE soam std</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -687,14 +675,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -749,18 +729,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1068,9 +1044,6 @@
   <dimension ref="A1:S136"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
@@ -1079,10 +1052,10 @@
     <col min="13" max="13" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.5" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.33203125" customWidth="1"/>
-    <col min="18" max="18" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
@@ -1134,13 +1107,13 @@
       <c r="P1" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="2" t="s">
         <v>204</v>
       </c>
       <c r="R1" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="2" t="s">
         <v>206</v>
       </c>
     </row>
@@ -1190,19 +1163,19 @@
       <c r="O2">
         <v>36.435325314601499</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="3">
         <f>ABS(H2-L2)/L2</f>
         <v>5.1953359436921409E-4</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="3">
         <f t="shared" ref="Q2:S17" si="0">ABS(I2-M2)/M2</f>
         <v>5.9528128046385721E-2</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="3">
         <f t="shared" si="0"/>
         <v>1.5064721596811148E-16</v>
       </c>
-      <c r="S2" s="5">
+      <c r="S2" s="3">
         <f t="shared" si="0"/>
         <v>4.0733366862865522E-3</v>
       </c>
@@ -1253,19 +1226,19 @@
       <c r="O3">
         <v>36.958372430213082</v>
       </c>
-      <c r="P3" s="5">
+      <c r="P3" s="3">
         <f t="shared" ref="P3:P66" si="1">ABS(H3-L3)/L3</f>
         <v>1.3498595692288911E-3</v>
       </c>
-      <c r="Q3" s="5">
+      <c r="Q3" s="3">
         <f t="shared" si="0"/>
         <v>1.1587176843589904E-2</v>
       </c>
-      <c r="R3" s="5">
+      <c r="R3" s="3">
         <f t="shared" si="0"/>
         <v>1.965601965070007E-3</v>
       </c>
-      <c r="S3" s="5">
+      <c r="S3" s="3">
         <f t="shared" si="0"/>
         <v>5.2970316682624096E-3</v>
       </c>
@@ -1316,19 +1289,19 @@
       <c r="O4">
         <v>37.769413268795837</v>
       </c>
-      <c r="P4" s="5">
+      <c r="P4" s="3">
         <f t="shared" si="1"/>
         <v>4.5952722483894107E-3</v>
       </c>
-      <c r="Q4" s="5">
+      <c r="Q4" s="3">
         <f t="shared" si="0"/>
         <v>4.1649059004414443E-2</v>
       </c>
-      <c r="R4" s="5">
+      <c r="R4" s="3">
         <f t="shared" si="0"/>
         <v>1.9646365422425964E-3</v>
       </c>
-      <c r="S4" s="5">
+      <c r="S4" s="3">
         <f t="shared" si="0"/>
         <v>5.3905413152894183E-3</v>
       </c>
@@ -1379,19 +1352,19 @@
       <c r="O5">
         <v>36.194344789513018</v>
       </c>
-      <c r="P5" s="5">
+      <c r="P5" s="3">
         <f t="shared" si="1"/>
         <v>4.5703084506090929E-3</v>
       </c>
-      <c r="Q5" s="5">
+      <c r="Q5" s="3">
         <f t="shared" si="0"/>
         <v>1.8925591353671806E-2</v>
       </c>
-      <c r="R5" s="5">
+      <c r="R5" s="3">
         <f t="shared" si="0"/>
         <v>1.9743336621406071E-3</v>
       </c>
-      <c r="S5" s="5">
+      <c r="S5" s="3">
         <f t="shared" si="0"/>
         <v>5.8343625140459864E-3</v>
       </c>
@@ -1442,19 +1415,19 @@
       <c r="O6">
         <v>37.501739090428842</v>
       </c>
-      <c r="P6" s="5">
+      <c r="P6" s="3">
         <f t="shared" si="1"/>
         <v>2.7306818254743495E-3</v>
       </c>
-      <c r="Q6" s="5">
+      <c r="Q6" s="3">
         <f t="shared" si="0"/>
         <v>1.8328787946576507E-2</v>
       </c>
-      <c r="R6" s="5">
+      <c r="R6" s="3">
         <f t="shared" si="0"/>
         <v>2.7548209368040161E-3</v>
       </c>
-      <c r="S6" s="5">
+      <c r="S6" s="3">
         <f t="shared" si="0"/>
         <v>7.031702825233921E-3</v>
       </c>
@@ -1505,19 +1478,19 @@
       <c r="O7">
         <v>37.462002988959028</v>
       </c>
-      <c r="P7" s="5">
+      <c r="P7" s="3">
         <f t="shared" si="1"/>
         <v>9.7469833243510415E-3</v>
       </c>
-      <c r="Q7" s="5">
+      <c r="Q7" s="3">
         <f t="shared" si="0"/>
         <v>5.5117824565136933E-2</v>
       </c>
-      <c r="R7" s="5">
+      <c r="R7" s="3">
         <f t="shared" si="0"/>
         <v>3.2282900801167414E-15</v>
       </c>
-      <c r="S7" s="5">
+      <c r="S7" s="3">
         <f t="shared" si="0"/>
         <v>7.9522875412921918E-4</v>
       </c>
@@ -1568,19 +1541,19 @@
       <c r="O8">
         <v>37.35412341458219</v>
       </c>
-      <c r="P8" s="5">
+      <c r="P8" s="3">
         <f t="shared" si="1"/>
         <v>1.4443472107919908E-3</v>
       </c>
-      <c r="Q8" s="5">
+      <c r="Q8" s="3">
         <f t="shared" si="0"/>
         <v>3.1972099391959864E-2</v>
       </c>
-      <c r="R8" s="5">
+      <c r="R8" s="3">
         <f t="shared" si="0"/>
         <v>5.9523809525430828E-3</v>
       </c>
-      <c r="S8" s="5">
+      <c r="S8" s="3">
         <f t="shared" si="0"/>
         <v>1.7392780146483874E-2</v>
       </c>
@@ -1631,19 +1604,19 @@
       <c r="O9">
         <v>34.195789594448122</v>
       </c>
-      <c r="P9" s="5">
+      <c r="P9" s="3">
         <f t="shared" si="1"/>
         <v>1.2799242694820847E-2</v>
       </c>
-      <c r="Q9" s="5">
+      <c r="Q9" s="3">
         <f t="shared" si="0"/>
         <v>4.7935053160129415E-2</v>
       </c>
-      <c r="R9" s="5">
+      <c r="R9" s="3">
         <f t="shared" si="0"/>
         <v>6.7251176498710071E-14</v>
       </c>
-      <c r="S9" s="5">
+      <c r="S9" s="3">
         <f t="shared" si="0"/>
         <v>1.4587899815648351E-3</v>
       </c>
@@ -1694,19 +1667,19 @@
       <c r="O10">
         <v>39.301506687818417</v>
       </c>
-      <c r="P10" s="5">
+      <c r="P10" s="3">
         <f t="shared" si="1"/>
         <v>6.5126716491227914E-3</v>
       </c>
-      <c r="Q10" s="5">
+      <c r="Q10" s="3">
         <f t="shared" si="0"/>
         <v>0.1967913024841684</v>
       </c>
-      <c r="R10" s="5">
+      <c r="R10" s="3">
         <f t="shared" si="0"/>
         <v>6.0842251154418198E-14</v>
       </c>
-      <c r="S10" s="5">
+      <c r="S10" s="3">
         <f t="shared" si="0"/>
         <v>1.8198377227304462E-3</v>
       </c>
@@ -1757,19 +1730,19 @@
       <c r="O11">
         <v>37.329377510878338</v>
       </c>
-      <c r="P11" s="5">
+      <c r="P11" s="3">
         <f t="shared" si="1"/>
         <v>6.410124902229624E-3</v>
       </c>
-      <c r="Q11" s="5">
+      <c r="Q11" s="3">
         <f t="shared" si="0"/>
         <v>4.6677072037569156E-2</v>
       </c>
-      <c r="R11" s="5">
+      <c r="R11" s="3">
         <f t="shared" si="0"/>
         <v>7.7220077218171377E-3</v>
       </c>
-      <c r="S11" s="5">
+      <c r="S11" s="3">
         <f t="shared" si="0"/>
         <v>2.2893538282407054E-2</v>
       </c>
@@ -1820,19 +1793,19 @@
       <c r="O12">
         <v>37.339594829959339</v>
       </c>
-      <c r="P12" s="5">
+      <c r="P12" s="3">
         <f t="shared" si="1"/>
         <v>3.2234887372657706E-4</v>
       </c>
-      <c r="Q12" s="5">
+      <c r="Q12" s="3">
         <f t="shared" si="0"/>
         <v>1.6424278609270817E-3</v>
       </c>
-      <c r="R12" s="5">
+      <c r="R12" s="3">
         <f t="shared" si="0"/>
         <v>3.9215686274752483E-3</v>
       </c>
-      <c r="S12" s="5">
+      <c r="S12" s="3">
         <f t="shared" si="0"/>
         <v>1.2814515996131159E-2</v>
       </c>
@@ -1883,19 +1856,19 @@
       <c r="O13">
         <v>35.878931011463131</v>
       </c>
-      <c r="P13" s="5">
+      <c r="P13" s="3">
         <f t="shared" si="1"/>
         <v>3.9074286662395975E-3</v>
       </c>
-      <c r="Q13" s="5">
+      <c r="Q13" s="3">
         <f t="shared" si="0"/>
         <v>5.6352509205287948E-2</v>
       </c>
-      <c r="R13" s="5">
+      <c r="R13" s="3">
         <f t="shared" si="0"/>
         <v>8.6302770843125992E-14</v>
       </c>
-      <c r="S13" s="5">
+      <c r="S13" s="3">
         <f t="shared" si="0"/>
         <v>2.2547943010228517E-3</v>
       </c>
@@ -1946,19 +1919,19 @@
       <c r="O14">
         <v>39.504477022629857</v>
       </c>
-      <c r="P14" s="5">
+      <c r="P14" s="3">
         <f t="shared" si="1"/>
         <v>2.2668152491909212E-2</v>
       </c>
-      <c r="Q14" s="5">
+      <c r="Q14" s="3">
         <f t="shared" si="0"/>
         <v>0.15884390611280222</v>
       </c>
-      <c r="R14" s="5">
+      <c r="R14" s="3">
         <f t="shared" si="0"/>
         <v>6.4171853140630278E-15</v>
       </c>
-      <c r="S14" s="5">
+      <c r="S14" s="3">
         <f t="shared" si="0"/>
         <v>2.1030517495693882E-3</v>
       </c>
@@ -2009,19 +1982,19 @@
       <c r="O15">
         <v>33.746377387411428</v>
       </c>
-      <c r="P15" s="5">
+      <c r="P15" s="3">
         <f t="shared" si="1"/>
         <v>1.8462584322256909E-2</v>
       </c>
-      <c r="Q15" s="5">
+      <c r="Q15" s="3">
         <f t="shared" si="0"/>
         <v>8.963929877505078E-2</v>
       </c>
-      <c r="R15" s="5">
+      <c r="R15" s="3">
         <f t="shared" si="0"/>
         <v>4.0983606554750611E-3</v>
       </c>
-      <c r="S15" s="5">
+      <c r="S15" s="3">
         <f t="shared" si="0"/>
         <v>1.5961586602364863E-2</v>
       </c>
@@ -2072,19 +2045,19 @@
       <c r="O16">
         <v>35.477481508356547</v>
       </c>
-      <c r="P16" s="5">
+      <c r="P16" s="3">
         <f t="shared" si="1"/>
         <v>3.3167136310409124E-3</v>
       </c>
-      <c r="Q16" s="5">
+      <c r="Q16" s="3">
         <f t="shared" si="0"/>
         <v>1.0609427078011591E-2</v>
       </c>
-      <c r="R16" s="5">
+      <c r="R16" s="3">
         <f t="shared" si="0"/>
         <v>2.5062922787319582E-13</v>
       </c>
-      <c r="S16" s="5">
+      <c r="S16" s="3">
         <f t="shared" si="0"/>
         <v>1.9102214193525791E-3</v>
       </c>
@@ -2135,19 +2108,19 @@
       <c r="O17">
         <v>37.296184811322853</v>
       </c>
-      <c r="P17" s="5">
+      <c r="P17" s="3">
         <f t="shared" si="1"/>
         <v>2.9867853863176962E-3</v>
       </c>
-      <c r="Q17" s="5">
+      <c r="Q17" s="3">
         <f t="shared" si="0"/>
         <v>5.5459646012112986E-2</v>
       </c>
-      <c r="R17" s="5">
+      <c r="R17" s="3">
         <f t="shared" si="0"/>
         <v>7.4626865673518856E-3</v>
       </c>
-      <c r="S17" s="5">
+      <c r="S17" s="3">
         <f t="shared" si="0"/>
         <v>1.9795969214551769E-2</v>
       </c>
@@ -2198,19 +2171,19 @@
       <c r="O18">
         <v>38.443556668482927</v>
       </c>
-      <c r="P18" s="5">
+      <c r="P18" s="3">
         <f t="shared" si="1"/>
         <v>2.9680079981992393E-3</v>
       </c>
-      <c r="Q18" s="5">
+      <c r="Q18" s="3">
         <f t="shared" ref="Q18:Q81" si="2">ABS(I18-M18)/M18</f>
         <v>1.4878013281071785E-2</v>
       </c>
-      <c r="R18" s="5">
+      <c r="R18" s="3">
         <f t="shared" ref="R18:R81" si="3">ABS(J18-N18)/N18</f>
         <v>3.6764705881810666E-3</v>
       </c>
-      <c r="S18" s="5">
+      <c r="S18" s="3">
         <f t="shared" ref="S18:S81" si="4">ABS(K18-O18)/O18</f>
         <v>8.8404947864684606E-3</v>
       </c>
@@ -2261,19 +2234,19 @@
       <c r="O19">
         <v>37.397353280584809</v>
       </c>
-      <c r="P19" s="5">
+      <c r="P19" s="3">
         <f t="shared" si="1"/>
         <v>1.3498393403975614E-2</v>
       </c>
-      <c r="Q19" s="5">
+      <c r="Q19" s="3">
         <f t="shared" si="2"/>
         <v>9.2741165452189009E-2</v>
       </c>
-      <c r="R19" s="5">
+      <c r="R19" s="3">
         <f t="shared" si="3"/>
         <v>5.0516662964820877E-14</v>
       </c>
-      <c r="S19" s="5">
+      <c r="S19" s="3">
         <f t="shared" si="4"/>
         <v>1.0851875146098958E-3</v>
       </c>
@@ -2324,19 +2297,19 @@
       <c r="O20">
         <v>36.435325314601499</v>
       </c>
-      <c r="P20" s="5">
+      <c r="P20" s="3">
         <f t="shared" si="1"/>
         <v>5.1953359436921409E-4</v>
       </c>
-      <c r="Q20" s="5">
+      <c r="Q20" s="3">
         <f t="shared" si="2"/>
         <v>5.9528128046385721E-2</v>
       </c>
-      <c r="R20" s="5">
+      <c r="R20" s="3">
         <f t="shared" si="3"/>
         <v>1.5064721596811148E-16</v>
       </c>
-      <c r="S20" s="5">
+      <c r="S20" s="3">
         <f t="shared" si="4"/>
         <v>4.0733366862865522E-3</v>
       </c>
@@ -2387,19 +2360,19 @@
       <c r="O21">
         <v>37.237509887261687</v>
       </c>
-      <c r="P21" s="5">
+      <c r="P21" s="3">
         <f t="shared" si="1"/>
         <v>3.9152779451042258E-3</v>
       </c>
-      <c r="Q21" s="5">
+      <c r="Q21" s="3">
         <f t="shared" si="2"/>
         <v>4.0584330928419725E-2</v>
       </c>
-      <c r="R21" s="5">
+      <c r="R21" s="3">
         <f t="shared" si="3"/>
         <v>1.2033694340984639E-3</v>
       </c>
-      <c r="S21" s="5">
+      <c r="S21" s="3">
         <f t="shared" si="4"/>
         <v>3.621082708915107E-3</v>
       </c>
@@ -2450,19 +2423,19 @@
       <c r="O22">
         <v>36.759781080951697</v>
       </c>
-      <c r="P22" s="5">
+      <c r="P22" s="3">
         <f t="shared" si="1"/>
         <v>3.9645928868142056E-4</v>
       </c>
-      <c r="Q22" s="5">
+      <c r="Q22" s="3">
         <f t="shared" si="2"/>
         <v>9.8340393327175945E-4</v>
       </c>
-      <c r="R22" s="5">
+      <c r="R22" s="3">
         <f t="shared" si="3"/>
         <v>2.5402201516953036E-3</v>
       </c>
-      <c r="S22" s="5">
+      <c r="S22" s="3">
         <f t="shared" si="4"/>
         <v>7.2652180891636733E-3</v>
       </c>
@@ -2513,19 +2486,19 @@
       <c r="O23">
         <v>37.18219267481016</v>
       </c>
-      <c r="P23" s="5">
+      <c r="P23" s="3">
         <f t="shared" si="1"/>
         <v>2.0280428325609442E-2</v>
       </c>
-      <c r="Q23" s="5">
+      <c r="Q23" s="3">
         <f t="shared" si="2"/>
         <v>5.4199263212694117E-2</v>
       </c>
-      <c r="R23" s="5">
+      <c r="R23" s="3">
         <f t="shared" si="3"/>
         <v>1.2235507450570107E-13</v>
       </c>
-      <c r="S23" s="5">
+      <c r="S23" s="3">
         <f t="shared" si="4"/>
         <v>2.2547943011575139E-3</v>
       </c>
@@ -2576,19 +2549,19 @@
       <c r="O24">
         <v>36.479984152248527</v>
       </c>
-      <c r="P24" s="5">
+      <c r="P24" s="3">
         <f t="shared" si="1"/>
         <v>8.2777174690720821E-4</v>
       </c>
-      <c r="Q24" s="5">
+      <c r="Q24" s="3">
         <f t="shared" si="2"/>
         <v>1.5000172232758659E-2</v>
       </c>
-      <c r="R24" s="5">
+      <c r="R24" s="3">
         <f t="shared" si="3"/>
         <v>1.0152284264033985E-2</v>
       </c>
-      <c r="S24" s="5">
+      <c r="S24" s="3">
         <f t="shared" si="4"/>
         <v>3.0094891916009957E-2</v>
       </c>
@@ -2639,19 +2612,19 @@
       <c r="O25">
         <v>33.376867471338393</v>
       </c>
-      <c r="P25" s="5">
+      <c r="P25" s="3">
         <f t="shared" si="1"/>
         <v>8.665591711373483E-3</v>
       </c>
-      <c r="Q25" s="5">
+      <c r="Q25" s="3">
         <f t="shared" si="2"/>
         <v>3.7012652426195128E-2</v>
       </c>
-      <c r="R25" s="5">
+      <c r="R25" s="3">
         <f t="shared" si="3"/>
         <v>9.4655520587216026E-14</v>
       </c>
-      <c r="S25" s="5">
+      <c r="S25" s="3">
         <f t="shared" si="4"/>
         <v>2.5157272558194591E-3</v>
       </c>
@@ -2702,19 +2675,19 @@
       <c r="O26">
         <v>38.359746602573942</v>
       </c>
-      <c r="P26" s="5">
+      <c r="P26" s="3">
         <f t="shared" si="1"/>
         <v>1.2273328304299341E-2</v>
       </c>
-      <c r="Q26" s="5">
+      <c r="Q26" s="3">
         <f t="shared" si="2"/>
         <v>2.4811630437476851E-2</v>
       </c>
-      <c r="R26" s="5">
+      <c r="R26" s="3">
         <f t="shared" si="3"/>
         <v>1.8225248127582006E-13</v>
       </c>
-      <c r="S26" s="5">
+      <c r="S26" s="3">
         <f t="shared" si="4"/>
         <v>2.3391844901440029E-3</v>
       </c>
@@ -2765,19 +2738,19 @@
       <c r="O27">
         <v>38.138837719899428</v>
       </c>
-      <c r="P27" s="5">
+      <c r="P27" s="3">
         <f t="shared" si="1"/>
         <v>6.2343959953500621E-3</v>
       </c>
-      <c r="Q27" s="5">
+      <c r="Q27" s="3">
         <f t="shared" si="2"/>
         <v>5.0470930265284097E-2</v>
       </c>
-      <c r="R27" s="5">
+      <c r="R27" s="3">
         <f t="shared" si="3"/>
         <v>8.4447325808333329E-14</v>
       </c>
-      <c r="S27" s="5">
+      <c r="S27" s="3">
         <f t="shared" si="4"/>
         <v>2.3391844900415423E-3</v>
       </c>
@@ -2828,19 +2801,19 @@
       <c r="O28">
         <v>35.48627646737981</v>
       </c>
-      <c r="P28" s="5">
+      <c r="P28" s="3">
         <f t="shared" si="1"/>
         <v>2.9015999481103776E-2</v>
       </c>
-      <c r="Q28" s="5">
+      <c r="Q28" s="3">
         <f t="shared" si="2"/>
         <v>0.15603246421711578</v>
       </c>
-      <c r="R28" s="5">
+      <c r="R28" s="3">
         <f t="shared" si="3"/>
         <v>4.5871559632034717E-3</v>
       </c>
-      <c r="S28" s="5">
+      <c r="S28" s="3">
         <f t="shared" si="4"/>
         <v>1.5434586937693817E-2</v>
       </c>
@@ -2891,19 +2864,19 @@
       <c r="O29">
         <v>36.213532229949507</v>
       </c>
-      <c r="P29" s="5">
+      <c r="P29" s="3">
         <f t="shared" si="1"/>
         <v>2.5376620169349513E-4</v>
       </c>
-      <c r="Q29" s="5">
+      <c r="Q29" s="3">
         <f t="shared" si="2"/>
         <v>1.0302233225348407E-3</v>
       </c>
-      <c r="R29" s="5">
+      <c r="R29" s="3">
         <f t="shared" si="3"/>
         <v>2.5906487782961448E-13</v>
       </c>
-      <c r="S29" s="5">
+      <c r="S29" s="3">
         <f t="shared" si="4"/>
         <v>2.2246968600482578E-3</v>
       </c>
@@ -2954,19 +2927,19 @@
       <c r="O30">
         <v>37.921979262926747</v>
       </c>
-      <c r="P30" s="5">
+      <c r="P30" s="3">
         <f t="shared" si="1"/>
         <v>3.5465200362180746E-3</v>
       </c>
-      <c r="Q30" s="5">
+      <c r="Q30" s="3">
         <f t="shared" si="2"/>
         <v>8.8729589940335831E-3</v>
       </c>
-      <c r="R30" s="5">
+      <c r="R30" s="3">
         <f t="shared" si="3"/>
         <v>8.6956521739064881E-3</v>
       </c>
-      <c r="S30" s="5">
+      <c r="S30" s="3">
         <f t="shared" si="4"/>
         <v>2.423509861188335E-2</v>
       </c>
@@ -3017,19 +2990,19 @@
       <c r="O31">
         <v>36.539746364821127</v>
       </c>
-      <c r="P31" s="5">
+      <c r="P31" s="3">
         <f t="shared" si="1"/>
         <v>2.3659280652637925E-5</v>
       </c>
-      <c r="Q31" s="5">
+      <c r="Q31" s="3">
         <f t="shared" si="2"/>
         <v>7.0297022256617225E-3</v>
       </c>
-      <c r="R31" s="5">
+      <c r="R31" s="3">
         <f t="shared" si="3"/>
         <v>1.2091898427395154E-3</v>
       </c>
-      <c r="S31" s="5">
+      <c r="S31" s="3">
         <f t="shared" si="4"/>
         <v>3.9079113014987912E-3</v>
       </c>
@@ -3080,19 +3053,19 @@
       <c r="O32">
         <v>36.453133337724033</v>
       </c>
-      <c r="P32" s="5">
+      <c r="P32" s="3">
         <f t="shared" si="1"/>
         <v>8.5787352173362311E-3</v>
       </c>
-      <c r="Q32" s="5">
+      <c r="Q32" s="3">
         <f t="shared" si="2"/>
         <v>2.7351454210529123E-2</v>
       </c>
-      <c r="R32" s="5">
+      <c r="R32" s="3">
         <f t="shared" si="3"/>
         <v>2.2446689112284612E-3</v>
       </c>
-      <c r="S32" s="5">
+      <c r="S32" s="3">
         <f t="shared" si="4"/>
         <v>6.5009009753507294E-3</v>
       </c>
@@ -3143,19 +3116,19 @@
       <c r="O33">
         <v>34.915971177853187</v>
       </c>
-      <c r="P33" s="5">
+      <c r="P33" s="3">
         <f t="shared" si="1"/>
         <v>3.5294062942277463E-4</v>
       </c>
-      <c r="Q33" s="5">
+      <c r="Q33" s="3">
         <f t="shared" si="2"/>
         <v>1.787023549792472E-2</v>
       </c>
-      <c r="R33" s="5">
+      <c r="R33" s="3">
         <f t="shared" si="3"/>
         <v>2.5125628140644967E-3</v>
       </c>
-      <c r="S33" s="5">
+      <c r="S33" s="3">
         <f t="shared" si="4"/>
         <v>9.0026418601889136E-3</v>
       </c>
@@ -3206,19 +3179,19 @@
       <c r="O34">
         <v>35.533359239771258</v>
       </c>
-      <c r="P34" s="5">
+      <c r="P34" s="3">
         <f t="shared" si="1"/>
         <v>1.4708361097130127E-2</v>
       </c>
-      <c r="Q34" s="5">
+      <c r="Q34" s="3">
         <f t="shared" si="2"/>
         <v>9.521222102734074E-2</v>
       </c>
-      <c r="R34" s="5">
+      <c r="R34" s="3">
         <f t="shared" si="3"/>
         <v>4.9720216908871136E-14</v>
       </c>
-      <c r="S34" s="5">
+      <c r="S34" s="3">
         <f t="shared" si="4"/>
         <v>1.1396015096108529E-3</v>
       </c>
@@ -3269,19 +3242,19 @@
       <c r="O35">
         <v>37.845288662281547</v>
       </c>
-      <c r="P35" s="5">
+      <c r="P35" s="3">
         <f t="shared" si="1"/>
         <v>9.1476165489321123E-3</v>
       </c>
-      <c r="Q35" s="5">
+      <c r="Q35" s="3">
         <f t="shared" si="2"/>
         <v>3.7578306431803467E-2</v>
       </c>
-      <c r="R35" s="5">
+      <c r="R35" s="3">
         <f t="shared" si="3"/>
         <v>2.6531845498602934E-13</v>
       </c>
-      <c r="S35" s="5">
+      <c r="S35" s="3">
         <f t="shared" si="4"/>
         <v>1.1661811547745058E-3</v>
       </c>
@@ -3332,19 +3305,19 @@
       <c r="O36">
         <v>37.660100261839567</v>
       </c>
-      <c r="P36" s="5">
+      <c r="P36" s="3">
         <f t="shared" si="1"/>
         <v>1.1920544021013538E-2</v>
       </c>
-      <c r="Q36" s="5">
+      <c r="Q36" s="3">
         <f t="shared" si="2"/>
         <v>2.8809237692503764E-2</v>
       </c>
-      <c r="R36" s="5">
+      <c r="R36" s="3">
         <f t="shared" si="3"/>
         <v>4.4444444444624708E-3</v>
       </c>
-      <c r="S36" s="5">
+      <c r="S36" s="3">
         <f t="shared" si="4"/>
         <v>1.2606750543025432E-2</v>
       </c>
@@ -3395,19 +3368,19 @@
       <c r="O37">
         <v>36.411923628817867</v>
       </c>
-      <c r="P37" s="5">
+      <c r="P37" s="3">
         <f t="shared" si="1"/>
         <v>2.3907521119116153E-3</v>
       </c>
-      <c r="Q37" s="5">
+      <c r="Q37" s="3">
         <f t="shared" si="2"/>
         <v>1.0685297748417401E-2</v>
       </c>
-      <c r="R37" s="5">
+      <c r="R37" s="3">
         <f t="shared" si="3"/>
         <v>1.7472335459092442E-3</v>
       </c>
-      <c r="S37" s="5">
+      <c r="S37" s="3">
         <f t="shared" si="4"/>
         <v>4.9734866545631017E-3</v>
       </c>
@@ -3458,19 +3431,19 @@
       <c r="O38">
         <v>37.35856627363053</v>
       </c>
-      <c r="P38" s="5">
+      <c r="P38" s="3">
         <f t="shared" si="1"/>
         <v>3.0182875949617801E-3</v>
       </c>
-      <c r="Q38" s="5">
+      <c r="Q38" s="3">
         <f t="shared" si="2"/>
         <v>9.8131197695757975E-3</v>
       </c>
-      <c r="R38" s="5">
+      <c r="R38" s="3">
         <f t="shared" si="3"/>
         <v>1.0031161267866392E-14</v>
       </c>
-      <c r="S38" s="5">
+      <c r="S38" s="3">
         <f t="shared" si="4"/>
         <v>1.7621159064499226E-3</v>
       </c>
@@ -3521,19 +3494,19 @@
       <c r="O39">
         <v>37.516954459697381</v>
       </c>
-      <c r="P39" s="5">
+      <c r="P39" s="3">
         <f t="shared" si="1"/>
         <v>7.9120723966310726E-3</v>
       </c>
-      <c r="Q39" s="5">
+      <c r="Q39" s="3">
         <f t="shared" si="2"/>
         <v>4.1318309648073984E-3</v>
       </c>
-      <c r="R39" s="5">
+      <c r="R39" s="3">
         <f t="shared" si="3"/>
         <v>2.8571428570927262E-3</v>
       </c>
-      <c r="S39" s="5">
+      <c r="S39" s="3">
         <f t="shared" si="4"/>
         <v>9.0647179678595841E-3</v>
       </c>
@@ -3584,19 +3557,19 @@
       <c r="O40">
         <v>35.997895585461748</v>
       </c>
-      <c r="P40" s="5">
+      <c r="P40" s="3">
         <f t="shared" si="1"/>
         <v>9.1415729690118228E-3</v>
       </c>
-      <c r="Q40" s="5">
+      <c r="Q40" s="3">
         <f t="shared" si="2"/>
         <v>1.3443454978492626E-2</v>
       </c>
-      <c r="R40" s="5">
+      <c r="R40" s="3">
         <f t="shared" si="3"/>
         <v>1.5020634474632364E-14</v>
       </c>
-      <c r="S40" s="5">
+      <c r="S40" s="3">
         <f t="shared" si="4"/>
         <v>1.8198377228430419E-3</v>
       </c>
@@ -3647,19 +3620,19 @@
       <c r="O41">
         <v>37.62145165485591</v>
       </c>
-      <c r="P41" s="5">
+      <c r="P41" s="3">
         <f t="shared" si="1"/>
         <v>5.2099547731840959E-5</v>
       </c>
-      <c r="Q41" s="5">
+      <c r="Q41" s="3">
         <f t="shared" si="2"/>
         <v>1.843070276527008E-2</v>
       </c>
-      <c r="R41" s="5">
+      <c r="R41" s="3">
         <f t="shared" si="3"/>
         <v>1.5527565120603833E-16</v>
       </c>
-      <c r="S41" s="5">
+      <c r="S41" s="3">
         <f t="shared" si="4"/>
         <v>1.7021288934936226E-3</v>
       </c>
@@ -3710,19 +3683,19 @@
       <c r="O42">
         <v>37.339297273981472</v>
       </c>
-      <c r="P42" s="5">
+      <c r="P42" s="3">
         <f t="shared" si="1"/>
         <v>4.3349336096544632E-3</v>
       </c>
-      <c r="Q42" s="5">
+      <c r="Q42" s="3">
         <f t="shared" si="2"/>
         <v>4.55122533591025E-3</v>
       </c>
-      <c r="R42" s="5">
+      <c r="R42" s="3">
         <f t="shared" si="3"/>
         <v>1.3999283689847166E-13</v>
       </c>
-      <c r="S42" s="5">
+      <c r="S42" s="3">
         <f t="shared" si="4"/>
         <v>2.6631205741258425E-3</v>
       </c>
@@ -3773,19 +3746,19 @@
       <c r="O43">
         <v>38.29307136542544</v>
       </c>
-      <c r="P43" s="5">
+      <c r="P43" s="3">
         <f t="shared" si="1"/>
         <v>1.5095980607567092E-2</v>
       </c>
-      <c r="Q43" s="5">
+      <c r="Q43" s="3">
         <f t="shared" si="2"/>
         <v>0.14002317091757693</v>
       </c>
-      <c r="R43" s="5">
+      <c r="R43" s="3">
         <f t="shared" si="3"/>
         <v>4.7687065854421102E-16</v>
       </c>
-      <c r="S43" s="5">
+      <c r="S43" s="3">
         <f t="shared" si="4"/>
         <v>1.3596199354301995E-3</v>
       </c>
@@ -3836,19 +3809,19 @@
       <c r="O44">
         <v>36.456607639899509</v>
       </c>
-      <c r="P44" s="5">
+      <c r="P44" s="3">
         <f t="shared" si="1"/>
         <v>2.7746946452911381E-3</v>
       </c>
-      <c r="Q44" s="5">
+      <c r="Q44" s="3">
         <f t="shared" si="2"/>
         <v>2.6585124897811882E-2</v>
       </c>
-      <c r="R44" s="5">
+      <c r="R44" s="3">
         <f t="shared" si="3"/>
         <v>2.3262544825494211E-14</v>
       </c>
-      <c r="S44" s="5">
+      <c r="S44" s="3">
         <f t="shared" si="4"/>
         <v>1.7021288936117948E-3</v>
       </c>
@@ -3899,19 +3872,19 @@
       <c r="O45">
         <v>33.708533342386708</v>
       </c>
-      <c r="P45" s="5">
+      <c r="P45" s="3">
         <f t="shared" si="1"/>
         <v>1.7693373866448189E-2</v>
       </c>
-      <c r="Q45" s="5">
+      <c r="Q45" s="3">
         <f t="shared" si="2"/>
         <v>0.14158815972146427</v>
       </c>
-      <c r="R45" s="5">
+      <c r="R45" s="3">
         <f t="shared" si="3"/>
         <v>1.0560036279754974E-13</v>
       </c>
-      <c r="S45" s="5">
+      <c r="S45" s="3">
         <f t="shared" si="4"/>
         <v>1.5026304509030764E-3</v>
       </c>
@@ -3962,19 +3935,19 @@
       <c r="O46">
         <v>37.99712462739199</v>
       </c>
-      <c r="P46" s="5">
+      <c r="P46" s="3">
         <f t="shared" si="1"/>
         <v>2.2925629842009353E-3</v>
       </c>
-      <c r="Q46" s="5">
+      <c r="Q46" s="3">
         <f t="shared" si="2"/>
         <v>1.335176313018604E-2</v>
       </c>
-      <c r="R46" s="5">
+      <c r="R46" s="3">
         <f t="shared" si="3"/>
         <v>6.3091482648909509E-3</v>
       </c>
-      <c r="S46" s="5">
+      <c r="S46" s="3">
         <f t="shared" si="4"/>
         <v>1.6631847429199681E-2</v>
       </c>
@@ -4025,19 +3998,19 @@
       <c r="O47">
         <v>27.094938103472249</v>
       </c>
-      <c r="P47" s="5">
+      <c r="P47" s="3">
         <f t="shared" si="1"/>
         <v>1.1980354162439342E-2</v>
       </c>
-      <c r="Q47" s="5">
+      <c r="Q47" s="3">
         <f t="shared" si="2"/>
         <v>9.1439699100083066E-2</v>
       </c>
-      <c r="R47" s="5">
+      <c r="R47" s="3">
         <f t="shared" si="3"/>
         <v>1.4478847929250027E-16</v>
       </c>
-      <c r="S47" s="5">
+      <c r="S47" s="3">
         <f t="shared" si="4"/>
         <v>7.8432583507786219E-3</v>
       </c>
@@ -4088,19 +4061,19 @@
       <c r="O48">
         <v>35.029003640580378</v>
       </c>
-      <c r="P48" s="5">
+      <c r="P48" s="3">
         <f t="shared" si="1"/>
         <v>1.2774752084548726E-3</v>
       </c>
-      <c r="Q48" s="5">
+      <c r="Q48" s="3">
         <f t="shared" si="2"/>
         <v>5.3411952886622628E-2</v>
       </c>
-      <c r="R48" s="5">
+      <c r="R48" s="3">
         <f t="shared" si="3"/>
         <v>4.9428129288856937E-13</v>
       </c>
-      <c r="S48" s="5">
+      <c r="S48" s="3">
         <f t="shared" si="4"/>
         <v>2.9784066187592929E-4</v>
       </c>
@@ -4151,19 +4124,19 @@
       <c r="O49">
         <v>34.653393218546682</v>
       </c>
-      <c r="P49" s="5">
+      <c r="P49" s="3">
         <f t="shared" si="1"/>
         <v>3.6946088101371768E-3</v>
       </c>
-      <c r="Q49" s="5">
+      <c r="Q49" s="3">
         <f t="shared" si="2"/>
         <v>4.5012718021617115E-3</v>
       </c>
-      <c r="R49" s="5">
+      <c r="R49" s="3">
         <f t="shared" si="3"/>
         <v>9.9629022990806179E-14</v>
       </c>
-      <c r="S49" s="5">
+      <c r="S49" s="3">
         <f t="shared" si="4"/>
         <v>5.8771677111211661E-4</v>
       </c>
@@ -4214,19 +4187,19 @@
       <c r="O50">
         <v>35.54286000844521</v>
       </c>
-      <c r="P50" s="5">
+      <c r="P50" s="3">
         <f t="shared" si="1"/>
         <v>2.232942147325858E-3</v>
       </c>
-      <c r="Q50" s="5">
+      <c r="Q50" s="3">
         <f t="shared" si="2"/>
         <v>9.4656011202877505E-2</v>
       </c>
-      <c r="R50" s="5">
+      <c r="R50" s="3">
         <f t="shared" si="3"/>
         <v>3.4038532768634513E-13</v>
       </c>
-      <c r="S50" s="5">
+      <c r="S50" s="3">
         <f t="shared" si="4"/>
         <v>6.0331830456840103E-4</v>
       </c>
@@ -4277,19 +4250,19 @@
       <c r="O51">
         <v>35.213088818013752</v>
       </c>
-      <c r="P51" s="5">
+      <c r="P51" s="3">
         <f t="shared" si="1"/>
         <v>7.4506827155631245E-3</v>
       </c>
-      <c r="Q51" s="5">
+      <c r="Q51" s="3">
         <f t="shared" si="2"/>
         <v>1.4489993035398264E-2</v>
       </c>
-      <c r="R51" s="5">
+      <c r="R51" s="3">
         <f t="shared" si="3"/>
         <v>1.4491548183514655E-14</v>
       </c>
-      <c r="S51" s="5">
+      <c r="S51" s="3">
         <f t="shared" si="4"/>
         <v>8.4352608863141551E-4</v>
       </c>
@@ -4340,19 +4313,19 @@
       <c r="O52">
         <v>34.603488874197083</v>
       </c>
-      <c r="P52" s="5">
+      <c r="P52" s="3">
         <f t="shared" si="1"/>
         <v>6.8476678086378468E-3</v>
       </c>
-      <c r="Q52" s="5">
+      <c r="Q52" s="3">
         <f t="shared" si="2"/>
         <v>8.3584933527874467E-3</v>
       </c>
-      <c r="R52" s="5">
+      <c r="R52" s="3">
         <f t="shared" si="3"/>
         <v>1.0767660119329105E-13</v>
       </c>
-      <c r="S52" s="5">
+      <c r="S52" s="3">
         <f t="shared" si="4"/>
         <v>9.3153257311150107E-4</v>
       </c>
@@ -4403,19 +4376,19 @@
       <c r="O53">
         <v>33.973336922117667</v>
       </c>
-      <c r="P53" s="5">
+      <c r="P53" s="3">
         <f t="shared" si="1"/>
         <v>8.5170939979155643E-3</v>
       </c>
-      <c r="Q53" s="5">
+      <c r="Q53" s="3">
         <f t="shared" si="2"/>
         <v>6.0747489500564073E-3</v>
       </c>
-      <c r="R53" s="5">
+      <c r="R53" s="3">
         <f t="shared" si="3"/>
         <v>4.0449910808320637E-14</v>
       </c>
-      <c r="S53" s="5">
+      <c r="S53" s="3">
         <f t="shared" si="4"/>
         <v>1.7873115264546663E-3</v>
       </c>
@@ -4466,19 +4439,19 @@
       <c r="O54">
         <v>35.505248633469563</v>
       </c>
-      <c r="P54" s="5">
+      <c r="P54" s="3">
         <f t="shared" si="1"/>
         <v>1.8077679496142716E-2</v>
       </c>
-      <c r="Q54" s="5">
+      <c r="Q54" s="3">
         <f t="shared" si="2"/>
         <v>0.22731556853857776</v>
       </c>
-      <c r="R54" s="5">
+      <c r="R54" s="3">
         <f t="shared" si="3"/>
         <v>1.4963718872264327E-13</v>
       </c>
-      <c r="S54" s="5">
+      <c r="S54" s="3">
         <f t="shared" si="4"/>
         <v>1.8604667271566852E-3</v>
       </c>
@@ -4529,19 +4502,19 @@
       <c r="O55">
         <v>35.12883602247377</v>
       </c>
-      <c r="P55" s="5">
+      <c r="P55" s="3">
         <f t="shared" si="1"/>
         <v>8.715151279893453E-3</v>
       </c>
-      <c r="Q55" s="5">
+      <c r="Q55" s="3">
         <f t="shared" si="2"/>
         <v>8.3084740018380902E-3</v>
       </c>
-      <c r="R55" s="5">
+      <c r="R55" s="3">
         <f t="shared" si="3"/>
         <v>1.4332116185627661E-13</v>
       </c>
-      <c r="S55" s="5">
+      <c r="S55" s="3">
         <f t="shared" si="4"/>
         <v>2.1953923300247853E-3</v>
       </c>
@@ -4592,19 +4565,19 @@
       <c r="O56">
         <v>32.35630290795568</v>
       </c>
-      <c r="P56" s="5">
+      <c r="P56" s="3">
         <f t="shared" si="1"/>
         <v>1.6296661994055321E-2</v>
       </c>
-      <c r="Q56" s="5">
+      <c r="Q56" s="3">
         <f t="shared" si="2"/>
         <v>1.0302849238215608E-2</v>
       </c>
-      <c r="R56" s="5">
+      <c r="R56" s="3">
         <f t="shared" si="3"/>
         <v>1.6253257609620642E-14</v>
       </c>
-      <c r="S56" s="5">
+      <c r="S56" s="3">
         <f t="shared" si="4"/>
         <v>2.4420060873948436E-3</v>
       </c>
@@ -4655,19 +4628,19 @@
       <c r="O57">
         <v>37.51191893320393</v>
       </c>
-      <c r="P57" s="5">
+      <c r="P57" s="3">
         <f t="shared" si="1"/>
         <v>7.9291172137217533E-3</v>
       </c>
-      <c r="Q57" s="5">
+      <c r="Q57" s="3">
         <f t="shared" si="2"/>
         <v>4.7952404859319217E-2</v>
       </c>
-      <c r="R57" s="5">
+      <c r="R57" s="3">
         <f t="shared" si="3"/>
         <v>1.1125223870268346E-13</v>
       </c>
-      <c r="S57" s="5">
+      <c r="S57" s="3">
         <f t="shared" si="4"/>
         <v>2.2246968600460825E-3</v>
       </c>
@@ -4718,19 +4691,19 @@
       <c r="O58">
         <v>35.132045382640626</v>
       </c>
-      <c r="P58" s="5">
+      <c r="P58" s="3">
         <f t="shared" si="1"/>
         <v>1.3518576765898982E-2</v>
       </c>
-      <c r="Q58" s="5">
+      <c r="Q58" s="3">
         <f t="shared" si="2"/>
         <v>2.9669711958083562E-2</v>
       </c>
-      <c r="R58" s="5">
+      <c r="R58" s="3">
         <f t="shared" si="3"/>
         <v>1.9794839347933149E-13</v>
       </c>
-      <c r="S58" s="5">
+      <c r="S58" s="3">
         <f t="shared" si="4"/>
         <v>2.4660949992457411E-3</v>
       </c>
@@ -4781,19 +4754,19 @@
       <c r="O59">
         <v>34.96052042999149</v>
       </c>
-      <c r="P59" s="5">
+      <c r="P59" s="3">
         <f t="shared" si="1"/>
         <v>8.4200775745848205E-3</v>
       </c>
-      <c r="Q59" s="5">
+      <c r="Q59" s="3">
         <f t="shared" si="2"/>
         <v>1.5743076386401329E-2</v>
       </c>
-      <c r="R59" s="5">
+      <c r="R59" s="3">
         <f t="shared" si="3"/>
         <v>3.0875108199879807E-13</v>
       </c>
-      <c r="S59" s="5">
+      <c r="S59" s="3">
         <f t="shared" si="4"/>
         <v>2.4067423582908036E-3</v>
       </c>
@@ -4844,19 +4817,19 @@
       <c r="O60">
         <v>35.497772700652497</v>
       </c>
-      <c r="P60" s="5">
+      <c r="P60" s="3">
         <f t="shared" si="1"/>
         <v>3.3410636904383827E-4</v>
       </c>
-      <c r="Q60" s="5">
+      <c r="Q60" s="3">
         <f t="shared" si="2"/>
         <v>0.29202863995465872</v>
       </c>
-      <c r="R60" s="5">
+      <c r="R60" s="3">
         <f t="shared" si="3"/>
         <v>1.0557833506523435E-13</v>
       </c>
-      <c r="S60" s="5">
+      <c r="S60" s="3">
         <f t="shared" si="4"/>
         <v>2.5284490523121927E-3</v>
       </c>
@@ -4907,19 +4880,19 @@
       <c r="O61">
         <v>33.637462200304277</v>
       </c>
-      <c r="P61" s="5">
+      <c r="P61" s="3">
         <f t="shared" si="1"/>
         <v>4.0026172263029703E-3</v>
       </c>
-      <c r="Q61" s="5">
+      <c r="Q61" s="3">
         <f t="shared" si="2"/>
         <v>6.703275452794386E-3</v>
       </c>
-      <c r="R61" s="5">
+      <c r="R61" s="3">
         <f t="shared" si="3"/>
         <v>5.1051620388919135E-13</v>
       </c>
-      <c r="S61" s="5">
+      <c r="S61" s="3">
         <f t="shared" si="4"/>
         <v>2.3837936164530131E-3</v>
       </c>
@@ -4970,19 +4943,19 @@
       <c r="O62">
         <v>37.097190118370861</v>
       </c>
-      <c r="P62" s="5">
+      <c r="P62" s="3">
         <f t="shared" si="1"/>
         <v>3.5759356222112644E-3</v>
       </c>
-      <c r="Q62" s="5">
+      <c r="Q62" s="3">
         <f t="shared" si="2"/>
         <v>6.1305750001617778E-3</v>
       </c>
-      <c r="R62" s="5">
+      <c r="R62" s="3">
         <f t="shared" si="3"/>
         <v>1.5386715848446437E-13</v>
       </c>
-      <c r="S62" s="5">
+      <c r="S62" s="3">
         <f t="shared" si="4"/>
         <v>2.3175002178763083E-3</v>
       </c>
@@ -5033,19 +5006,19 @@
       <c r="O63">
         <v>36.121933465166698</v>
       </c>
-      <c r="P63" s="5">
+      <c r="P63" s="3">
         <f t="shared" si="1"/>
         <v>4.3966119518210637E-3</v>
       </c>
-      <c r="Q63" s="5">
+      <c r="Q63" s="3">
         <f t="shared" si="2"/>
         <v>5.5730445895561583E-3</v>
       </c>
-      <c r="R63" s="5">
+      <c r="R63" s="3">
         <f t="shared" si="3"/>
         <v>6.5805531619835152E-14</v>
       </c>
-      <c r="S63" s="5">
+      <c r="S63" s="3">
         <f t="shared" si="4"/>
         <v>1.1422048274419068E-3</v>
       </c>
@@ -5096,19 +5069,19 @@
       <c r="O64">
         <v>34.458683324094608</v>
       </c>
-      <c r="P64" s="5">
+      <c r="P64" s="3">
         <f t="shared" si="1"/>
         <v>6.8910756553712451E-3</v>
       </c>
-      <c r="Q64" s="5">
+      <c r="Q64" s="3">
         <f t="shared" si="2"/>
         <v>1.9533615426277809E-2</v>
       </c>
-      <c r="R64" s="5">
+      <c r="R64" s="3">
         <f t="shared" si="3"/>
         <v>1.2455901285987472E-13</v>
       </c>
-      <c r="S64" s="5">
+      <c r="S64" s="3">
         <f t="shared" si="4"/>
         <v>1.2084596562087276E-3</v>
       </c>
@@ -5159,19 +5132,19 @@
       <c r="O65">
         <v>27.094938103472249</v>
       </c>
-      <c r="P65" s="5">
+      <c r="P65" s="3">
         <f t="shared" si="1"/>
         <v>1.1980354162439342E-2</v>
       </c>
-      <c r="Q65" s="5">
+      <c r="Q65" s="3">
         <f t="shared" si="2"/>
         <v>9.1439699100083066E-2</v>
       </c>
-      <c r="R65" s="5">
+      <c r="R65" s="3">
         <f t="shared" si="3"/>
         <v>1.4478847929250027E-16</v>
       </c>
-      <c r="S65" s="5">
+      <c r="S65" s="3">
         <f t="shared" si="4"/>
         <v>7.8432583507786219E-3</v>
       </c>
@@ -5222,19 +5195,19 @@
       <c r="O66">
         <v>34.718292413323788</v>
       </c>
-      <c r="P66" s="5">
+      <c r="P66" s="3">
         <f t="shared" si="1"/>
         <v>4.7962368192668581E-3</v>
       </c>
-      <c r="Q66" s="5">
+      <c r="Q66" s="3">
         <f t="shared" si="2"/>
         <v>5.513317823186344E-3</v>
       </c>
-      <c r="R66" s="5">
+      <c r="R66" s="3">
         <f t="shared" si="3"/>
         <v>4.031721485535431E-13</v>
       </c>
-      <c r="S66" s="5">
+      <c r="S66" s="3">
         <f t="shared" si="4"/>
         <v>7.5329577524999762E-4</v>
       </c>
@@ -5285,19 +5258,19 @@
       <c r="O67">
         <v>35.468101381387683</v>
       </c>
-      <c r="P67" s="5">
+      <c r="P67" s="3">
         <f t="shared" ref="P67:P130" si="5">ABS(H67-L67)/L67</f>
         <v>5.1677477577130671E-3</v>
       </c>
-      <c r="Q67" s="5">
+      <c r="Q67" s="3">
         <f t="shared" si="2"/>
         <v>5.851001504336651E-2</v>
       </c>
-      <c r="R67" s="5">
+      <c r="R67" s="3">
         <f t="shared" si="3"/>
         <v>5.5611361550320019E-13</v>
       </c>
-      <c r="S67" s="5">
+      <c r="S67" s="3">
         <f t="shared" si="4"/>
         <v>4.9370528827334149E-4</v>
       </c>
@@ -5348,19 +5321,19 @@
       <c r="O68">
         <v>35.409370338241111</v>
       </c>
-      <c r="P68" s="5">
+      <c r="P68" s="3">
         <f t="shared" si="5"/>
         <v>2.8945794285650142E-3</v>
       </c>
-      <c r="Q68" s="5">
+      <c r="Q68" s="3">
         <f t="shared" si="2"/>
         <v>6.4323183371843293E-3</v>
       </c>
-      <c r="R68" s="5">
+      <c r="R68" s="3">
         <f t="shared" si="3"/>
         <v>8.5601516281687337E-14</v>
       </c>
-      <c r="S68" s="5">
+      <c r="S68" s="3">
         <f t="shared" si="4"/>
         <v>2.3952130201735969E-3</v>
       </c>
@@ -5411,19 +5384,19 @@
       <c r="O69">
         <v>34.719994672776352</v>
       </c>
-      <c r="P69" s="5">
+      <c r="P69" s="3">
         <f t="shared" si="5"/>
         <v>1.9119425451063134E-2</v>
       </c>
-      <c r="Q69" s="5">
+      <c r="Q69" s="3">
         <f t="shared" si="2"/>
         <v>1.3701624157438457E-2</v>
       </c>
-      <c r="R69" s="5">
+      <c r="R69" s="3">
         <f t="shared" si="3"/>
         <v>1.3151091646016364E-13</v>
       </c>
-      <c r="S69" s="5">
+      <c r="S69" s="3">
         <f t="shared" si="4"/>
         <v>2.7359832392160098E-3</v>
       </c>
@@ -5474,19 +5447,19 @@
       <c r="O70">
         <v>35.806763728112728</v>
       </c>
-      <c r="P70" s="5">
+      <c r="P70" s="3">
         <f t="shared" si="5"/>
         <v>4.5823884003298229E-3</v>
       </c>
-      <c r="Q70" s="5">
+      <c r="Q70" s="3">
         <f t="shared" si="2"/>
         <v>9.4363624010251647E-3</v>
       </c>
-      <c r="R70" s="5">
+      <c r="R70" s="3">
         <f t="shared" si="3"/>
         <v>1.3897616854220075E-14</v>
       </c>
-      <c r="S70" s="5">
+      <c r="S70" s="3">
         <f t="shared" si="4"/>
         <v>2.5542825872525579E-3</v>
       </c>
@@ -5537,19 +5510,19 @@
       <c r="O71">
         <v>34.704324927868512</v>
       </c>
-      <c r="P71" s="5">
+      <c r="P71" s="3">
         <f t="shared" si="5"/>
         <v>1.9930461398523322E-2</v>
       </c>
-      <c r="Q71" s="5">
+      <c r="Q71" s="3">
         <f t="shared" si="2"/>
         <v>7.7897187398121473E-2</v>
       </c>
-      <c r="R71" s="5">
+      <c r="R71" s="3">
         <f t="shared" si="3"/>
         <v>2.1078438141088069E-13</v>
       </c>
-      <c r="S71" s="5">
+      <c r="S71" s="3">
         <f t="shared" si="4"/>
         <v>2.5940380918208703E-3</v>
       </c>
@@ -5600,19 +5573,19 @@
       <c r="O72">
         <v>35.003417054625103</v>
       </c>
-      <c r="P72" s="5">
+      <c r="P72" s="3">
         <f t="shared" si="5"/>
         <v>8.4517576723572036E-3</v>
       </c>
-      <c r="Q72" s="5">
+      <c r="Q72" s="3">
         <f t="shared" si="2"/>
         <v>1.7363664605030579E-2</v>
       </c>
-      <c r="R72" s="5">
+      <c r="R72" s="3">
         <f t="shared" si="3"/>
         <v>1.5111084238391049E-13</v>
       </c>
-      <c r="S72" s="5">
+      <c r="S72" s="3">
         <f t="shared" si="4"/>
         <v>2.3724825831885317E-3</v>
       </c>
@@ -5663,19 +5636,19 @@
       <c r="O73">
         <v>36.578317531619547</v>
       </c>
-      <c r="P73" s="5">
+      <c r="P73" s="3">
         <f t="shared" si="5"/>
         <v>3.7992490506828349E-3</v>
       </c>
-      <c r="Q73" s="5">
+      <c r="Q73" s="3">
         <f t="shared" si="2"/>
         <v>0.2328890443006808</v>
       </c>
-      <c r="R73" s="5">
+      <c r="R73" s="3">
         <f t="shared" si="3"/>
         <v>9.3696613365643976E-14</v>
       </c>
-      <c r="S73" s="5">
+      <c r="S73" s="3">
         <f t="shared" si="4"/>
         <v>2.7063649080155501E-3</v>
       </c>
@@ -5726,19 +5699,19 @@
       <c r="O74">
         <v>36.687137888703688</v>
       </c>
-      <c r="P74" s="5">
+      <c r="P74" s="3">
         <f t="shared" si="5"/>
         <v>4.9575003510076024E-3</v>
       </c>
-      <c r="Q74" s="5">
+      <c r="Q74" s="3">
         <f t="shared" si="2"/>
         <v>8.6000833206051949E-3</v>
       </c>
-      <c r="R74" s="5">
+      <c r="R74" s="3">
         <f t="shared" si="3"/>
         <v>1.1428571427917316E-2</v>
       </c>
-      <c r="S74" s="5">
+      <c r="S74" s="3">
         <f t="shared" si="4"/>
         <v>3.325555374134663E-2</v>
       </c>
@@ -5789,19 +5762,19 @@
       <c r="O75">
         <v>39.609137149689978</v>
       </c>
-      <c r="P75" s="5">
+      <c r="P75" s="3">
         <f t="shared" si="5"/>
         <v>1.0593587898468825E-2</v>
       </c>
-      <c r="Q75" s="5">
+      <c r="Q75" s="3">
         <f t="shared" si="2"/>
         <v>3.7959218004732689E-2</v>
       </c>
-      <c r="R75" s="5">
+      <c r="R75" s="3">
         <f t="shared" si="3"/>
         <v>1.6180994798322425E-13</v>
       </c>
-      <c r="S75" s="5">
+      <c r="S75" s="3">
         <f t="shared" si="4"/>
         <v>2.8943620760940765E-3</v>
       </c>
@@ -5852,19 +5825,19 @@
       <c r="O76">
         <v>35.158760815201163</v>
       </c>
-      <c r="P76" s="5">
+      <c r="P76" s="3">
         <f t="shared" si="5"/>
         <v>1.2650506638845929E-3</v>
       </c>
-      <c r="Q76" s="5">
+      <c r="Q76" s="3">
         <f t="shared" si="2"/>
         <v>8.4732171382562128E-4</v>
       </c>
-      <c r="R76" s="5">
+      <c r="R76" s="3">
         <f t="shared" si="3"/>
         <v>2.0154239732336076E-13</v>
       </c>
-      <c r="S76" s="5">
+      <c r="S76" s="3">
         <f t="shared" si="4"/>
         <v>6.4871884857626791E-4</v>
       </c>
@@ -5915,19 +5888,19 @@
       <c r="O77">
         <v>37.295513880245629</v>
       </c>
-      <c r="P77" s="5">
+      <c r="P77" s="3">
         <f t="shared" si="5"/>
         <v>2.9839531908383244E-3</v>
       </c>
-      <c r="Q77" s="5">
+      <c r="Q77" s="3">
         <f t="shared" si="2"/>
         <v>0.12116647791330826</v>
       </c>
-      <c r="R77" s="5">
+      <c r="R77" s="3">
         <f t="shared" si="3"/>
         <v>2.6990553306111388E-3</v>
       </c>
-      <c r="S77" s="5">
+      <c r="S77" s="3">
         <f t="shared" si="4"/>
         <v>7.3242930531002854E-3</v>
       </c>
@@ -5978,19 +5951,19 @@
       <c r="O78">
         <v>34.936145748779388</v>
       </c>
-      <c r="P78" s="5">
+      <c r="P78" s="3">
         <f t="shared" si="5"/>
         <v>7.013848146203993E-3</v>
       </c>
-      <c r="Q78" s="5">
+      <c r="Q78" s="3">
         <f t="shared" si="2"/>
         <v>8.9301782677527614E-3</v>
       </c>
-      <c r="R78" s="5">
+      <c r="R78" s="3">
         <f t="shared" si="3"/>
         <v>3.3198389343035451E-13</v>
       </c>
-      <c r="S78" s="5">
+      <c r="S78" s="3">
         <f t="shared" si="4"/>
         <v>1.3306725783965789E-3</v>
       </c>
@@ -6041,19 +6014,19 @@
       <c r="O79">
         <v>36.926722583592657</v>
       </c>
-      <c r="P79" s="5">
+      <c r="P79" s="3">
         <f t="shared" si="5"/>
         <v>1.7524143946841882E-3</v>
       </c>
-      <c r="Q79" s="5">
+      <c r="Q79" s="3">
         <f t="shared" si="2"/>
         <v>0.15198337118248526</v>
       </c>
-      <c r="R79" s="5">
+      <c r="R79" s="3">
         <f t="shared" si="3"/>
         <v>5.4945054944890766E-3</v>
       </c>
-      <c r="S79" s="5">
+      <c r="S79" s="3">
         <f t="shared" si="4"/>
         <v>1.5128372510160424E-2</v>
       </c>
@@ -6104,19 +6077,19 @@
       <c r="O80">
         <v>34.502143106978401</v>
       </c>
-      <c r="P80" s="5">
+      <c r="P80" s="3">
         <f t="shared" si="5"/>
         <v>5.1898386158856528E-3</v>
       </c>
-      <c r="Q80" s="5">
+      <c r="Q80" s="3">
         <f t="shared" si="2"/>
         <v>4.0600679851189314E-2</v>
       </c>
-      <c r="R80" s="5">
+      <c r="R80" s="3">
         <f t="shared" si="3"/>
         <v>1.8435039424467505E-13</v>
       </c>
-      <c r="S80" s="5">
+      <c r="S80" s="3">
         <f t="shared" si="4"/>
         <v>1.2353309230235499E-3</v>
       </c>
@@ -6167,19 +6140,19 @@
       <c r="O81">
         <v>37.443640085176831</v>
       </c>
-      <c r="P81" s="5">
+      <c r="P81" s="3">
         <f t="shared" si="5"/>
         <v>1.8560566808563169E-3</v>
       </c>
-      <c r="Q81" s="5">
+      <c r="Q81" s="3">
         <f t="shared" si="2"/>
         <v>1.4524694299784343E-2</v>
       </c>
-      <c r="R81" s="5">
+      <c r="R81" s="3">
         <f t="shared" si="3"/>
         <v>7.7267526705256845E-14</v>
       </c>
-      <c r="S81" s="5">
+      <c r="S81" s="3">
         <f t="shared" si="4"/>
         <v>1.3236273173554221E-3</v>
       </c>
@@ -6230,19 +6203,19 @@
       <c r="O82">
         <v>36.231536466918342</v>
       </c>
-      <c r="P82" s="5">
+      <c r="P82" s="3">
         <f t="shared" si="5"/>
         <v>9.7790820104306391E-4</v>
       </c>
-      <c r="Q82" s="5">
+      <c r="Q82" s="3">
         <f t="shared" ref="Q82:Q136" si="6">ABS(I82-M82)/M82</f>
         <v>6.079750297184882E-2</v>
       </c>
-      <c r="R82" s="5">
+      <c r="R82" s="3">
         <f t="shared" ref="R82:R136" si="7">ABS(J82-N82)/N82</f>
         <v>1.3253810463624597E-3</v>
       </c>
-      <c r="S82" s="5">
+      <c r="S82" s="3">
         <f t="shared" ref="S82:S136" si="8">ABS(K82-O82)/O82</f>
         <v>4.0182648882576789E-3</v>
       </c>
@@ -6293,19 +6266,19 @@
       <c r="O83">
         <v>37.055289543196871</v>
       </c>
-      <c r="P83" s="5">
+      <c r="P83" s="3">
         <f t="shared" si="5"/>
         <v>7.8636205641206911E-3</v>
       </c>
-      <c r="Q83" s="5">
+      <c r="Q83" s="3">
         <f t="shared" si="6"/>
         <v>1.2658620134973082E-2</v>
       </c>
-      <c r="R83" s="5">
+      <c r="R83" s="3">
         <f t="shared" si="7"/>
         <v>4.1131388641156154E-14</v>
       </c>
-      <c r="S83" s="5">
+      <c r="S83" s="3">
         <f t="shared" si="8"/>
         <v>1.9249296000098202E-3</v>
       </c>
@@ -6356,19 +6329,19 @@
       <c r="O84">
         <v>35.373199375798791</v>
       </c>
-      <c r="P84" s="5">
+      <c r="P84" s="3">
         <f t="shared" si="5"/>
         <v>1.3044993220736018E-2</v>
       </c>
-      <c r="Q84" s="5">
+      <c r="Q84" s="3">
         <f t="shared" si="6"/>
         <v>2.4194110449826771E-2</v>
       </c>
-      <c r="R84" s="5">
+      <c r="R84" s="3">
         <f t="shared" si="7"/>
         <v>9.5300973279799954E-14</v>
       </c>
-      <c r="S84" s="5">
+      <c r="S84" s="3">
         <f t="shared" si="8"/>
         <v>1.8264855429023083E-3</v>
       </c>
@@ -6419,19 +6392,19 @@
       <c r="O85">
         <v>32.852395547004747</v>
       </c>
-      <c r="P85" s="5">
+      <c r="P85" s="3">
         <f t="shared" si="5"/>
         <v>9.6581375205126285E-3</v>
       </c>
-      <c r="Q85" s="5">
+      <c r="Q85" s="3">
         <f t="shared" si="6"/>
         <v>6.8610393335745826E-2</v>
       </c>
-      <c r="R85" s="5">
+      <c r="R85" s="3">
         <f t="shared" si="7"/>
         <v>8.3555103438590158E-14</v>
       </c>
-      <c r="S85" s="5">
+      <c r="S85" s="3">
         <f t="shared" si="8"/>
         <v>1.7559276056652541E-3</v>
       </c>
@@ -6482,19 +6455,19 @@
       <c r="O86">
         <v>35.593782270321917</v>
       </c>
-      <c r="P86" s="5">
+      <c r="P86" s="3">
         <f t="shared" si="5"/>
         <v>2.6019458501608168E-3</v>
       </c>
-      <c r="Q86" s="5">
+      <c r="Q86" s="3">
         <f t="shared" si="6"/>
         <v>8.8896000794495172E-4</v>
       </c>
-      <c r="R86" s="5">
+      <c r="R86" s="3">
         <f t="shared" si="7"/>
         <v>8.8207360044162749E-14</v>
       </c>
-      <c r="S86" s="5">
+      <c r="S86" s="3">
         <f t="shared" si="8"/>
         <v>1.7746242911743366E-3</v>
       </c>
@@ -6545,19 +6518,19 @@
       <c r="O87">
         <v>29.543429716645221</v>
       </c>
-      <c r="P87" s="5">
+      <c r="P87" s="3">
         <f t="shared" si="5"/>
         <v>2.6023986575110313E-4</v>
       </c>
-      <c r="Q87" s="5">
+      <c r="Q87" s="3">
         <f t="shared" si="6"/>
         <v>6.7623399680982563E-2</v>
       </c>
-      <c r="R87" s="5">
+      <c r="R87" s="3">
         <f t="shared" si="7"/>
         <v>5.5966600971341554E-14</v>
       </c>
-      <c r="S87" s="5">
+      <c r="S87" s="3">
         <f t="shared" si="8"/>
         <v>4.2105450168815626E-3</v>
       </c>
@@ -6608,19 +6581,19 @@
       <c r="O88">
         <v>39.604287220083968</v>
       </c>
-      <c r="P88" s="5">
+      <c r="P88" s="3">
         <f t="shared" si="5"/>
         <v>3.5618640076261875E-3</v>
       </c>
-      <c r="Q88" s="5">
+      <c r="Q88" s="3">
         <f t="shared" si="6"/>
         <v>5.555681397121532E-2</v>
       </c>
-      <c r="R88" s="5">
+      <c r="R88" s="3">
         <f t="shared" si="7"/>
         <v>2.1140286776588685E-14</v>
       </c>
-      <c r="S88" s="5">
+      <c r="S88" s="3">
         <f t="shared" si="8"/>
         <v>1.7873115269540667E-3</v>
       </c>
@@ -6671,19 +6644,19 @@
       <c r="O89">
         <v>33.968326799874362</v>
       </c>
-      <c r="P89" s="5">
+      <c r="P89" s="3">
         <f t="shared" si="5"/>
         <v>3.3718581649098459E-3</v>
       </c>
-      <c r="Q89" s="5">
+      <c r="Q89" s="3">
         <f t="shared" si="6"/>
         <v>2.9363144442861134E-2</v>
       </c>
-      <c r="R89" s="5">
+      <c r="R89" s="3">
         <f t="shared" si="7"/>
         <v>1.4575769789086413E-14</v>
       </c>
-      <c r="S89" s="5">
+      <c r="S89" s="3">
         <f t="shared" si="8"/>
         <v>1.9550360831105339E-3</v>
       </c>
@@ -6734,19 +6707,19 @@
       <c r="O90">
         <v>35.525282651959678</v>
       </c>
-      <c r="P90" s="5">
+      <c r="P90" s="3">
         <f t="shared" si="5"/>
         <v>1.5347844592901522E-2</v>
       </c>
-      <c r="Q90" s="5">
+      <c r="Q90" s="3">
         <f t="shared" si="6"/>
         <v>0.22885199040031126</v>
       </c>
-      <c r="R90" s="5">
+      <c r="R90" s="3">
         <f t="shared" si="7"/>
         <v>2.2626880167747982E-13</v>
       </c>
-      <c r="S90" s="5">
+      <c r="S90" s="3">
         <f t="shared" si="8"/>
         <v>1.8604667278008258E-3</v>
       </c>
@@ -6797,19 +6770,19 @@
       <c r="O91">
         <v>36.102814722620998</v>
       </c>
-      <c r="P91" s="5">
+      <c r="P91" s="3">
         <f t="shared" si="5"/>
         <v>7.4645666680089647E-3</v>
       </c>
-      <c r="Q91" s="5">
+      <c r="Q91" s="3">
         <f t="shared" si="6"/>
         <v>1.6732399571189941E-2</v>
       </c>
-      <c r="R91" s="5">
+      <c r="R91" s="3">
         <f t="shared" si="7"/>
         <v>1.0588774345540154E-13</v>
       </c>
-      <c r="S91" s="5">
+      <c r="S91" s="3">
         <f t="shared" si="8"/>
         <v>2.0768454402135773E-3</v>
       </c>
@@ -6860,19 +6833,19 @@
       <c r="O92">
         <v>35.996457635572632</v>
       </c>
-      <c r="P92" s="5">
+      <c r="P92" s="3">
         <f t="shared" si="5"/>
         <v>1.9925292680057879E-2</v>
       </c>
-      <c r="Q92" s="5">
+      <c r="Q92" s="3">
         <f t="shared" si="6"/>
         <v>5.9494918280453675E-2</v>
       </c>
-      <c r="R92" s="5">
+      <c r="R92" s="3">
         <f t="shared" si="7"/>
         <v>1.0752688172042897E-2</v>
       </c>
-      <c r="S92" s="5">
+      <c r="S92" s="3">
         <f t="shared" si="8"/>
         <v>4.10579814622909E-2</v>
       </c>
@@ -6923,19 +6896,19 @@
       <c r="O93">
         <v>35.705545532791163</v>
       </c>
-      <c r="P93" s="5">
+      <c r="P93" s="3">
         <f t="shared" si="5"/>
         <v>3.701451591485268E-3</v>
       </c>
-      <c r="Q93" s="5">
+      <c r="Q93" s="3">
         <f t="shared" si="6"/>
         <v>3.9611602994079516E-2</v>
       </c>
-      <c r="R93" s="5">
+      <c r="R93" s="3">
         <f t="shared" si="7"/>
         <v>2.365930598709693E-3</v>
       </c>
-      <c r="S93" s="5">
+      <c r="S93" s="3">
         <f t="shared" si="8"/>
         <v>7.5785579946259013E-3</v>
       </c>
@@ -6986,19 +6959,19 @@
       <c r="O94">
         <v>35.856329131837477</v>
       </c>
-      <c r="P94" s="5">
+      <c r="P94" s="3">
         <f t="shared" si="5"/>
         <v>1.2139325267282548E-2</v>
       </c>
-      <c r="Q94" s="5">
+      <c r="Q94" s="3">
         <f t="shared" si="6"/>
         <v>2.1900926583046262E-2</v>
       </c>
-      <c r="R94" s="5">
+      <c r="R94" s="3">
         <f t="shared" si="7"/>
         <v>1.8484288355033252E-3</v>
       </c>
-      <c r="S94" s="5">
+      <c r="S94" s="3">
         <f t="shared" si="8"/>
         <v>6.654795102948554E-3</v>
       </c>
@@ -7049,19 +7022,19 @@
       <c r="O95">
         <v>35.79810678594545</v>
       </c>
-      <c r="P95" s="5">
+      <c r="P95" s="3">
         <f t="shared" si="5"/>
         <v>7.6839177026243749E-4</v>
       </c>
-      <c r="Q95" s="5">
+      <c r="Q95" s="3">
         <f t="shared" si="6"/>
         <v>2.7452065924477985E-2</v>
       </c>
-      <c r="R95" s="5">
+      <c r="R95" s="3">
         <f t="shared" si="7"/>
         <v>2.7397260272446567E-3</v>
       </c>
-      <c r="S95" s="5">
+      <c r="S95" s="3">
         <f t="shared" si="8"/>
         <v>8.7403549353895042E-3</v>
       </c>
@@ -7112,19 +7085,19 @@
       <c r="O96">
         <v>34.571116320511628</v>
       </c>
-      <c r="P96" s="5">
+      <c r="P96" s="3">
         <f t="shared" si="5"/>
         <v>1.0949161218908774E-2</v>
       </c>
-      <c r="Q96" s="5">
+      <c r="Q96" s="3">
         <f t="shared" si="6"/>
         <v>1.5046328248413551E-2</v>
       </c>
-      <c r="R96" s="5">
+      <c r="R96" s="3">
         <f t="shared" si="7"/>
         <v>6.9963789274504629E-14</v>
       </c>
-      <c r="S96" s="5">
+      <c r="S96" s="3">
         <f t="shared" si="8"/>
         <v>1.1474473084771403E-3</v>
       </c>
@@ -7175,19 +7148,19 @@
       <c r="O97">
         <v>35.491706888282494</v>
       </c>
-      <c r="P97" s="5">
+      <c r="P97" s="3">
         <f t="shared" si="5"/>
         <v>2.4179564615027503E-3</v>
       </c>
-      <c r="Q97" s="5">
+      <c r="Q97" s="3">
         <f t="shared" si="6"/>
         <v>0.1183594226932584</v>
       </c>
-      <c r="R97" s="5">
+      <c r="R97" s="3">
         <f t="shared" si="7"/>
         <v>8.0000000000594543E-3</v>
       </c>
-      <c r="S97" s="5">
+      <c r="S97" s="3">
         <f t="shared" si="8"/>
         <v>2.7230256767295302E-2</v>
       </c>
@@ -7238,19 +7211,19 @@
       <c r="O98">
         <v>36.872291478585339</v>
       </c>
-      <c r="P98" s="5">
+      <c r="P98" s="3">
         <f t="shared" si="5"/>
         <v>2.417569971225789E-2</v>
       </c>
-      <c r="Q98" s="5">
+      <c r="Q98" s="3">
         <f t="shared" si="6"/>
         <v>0.10381015849336564</v>
       </c>
-      <c r="R98" s="5">
+      <c r="R98" s="3">
         <f t="shared" si="7"/>
         <v>2.5382168498563548E-13</v>
       </c>
-      <c r="S98" s="5">
+      <c r="S98" s="3">
         <f t="shared" si="8"/>
         <v>2.7063649096751652E-3</v>
       </c>
@@ -7301,19 +7274,19 @@
       <c r="O99">
         <v>35.012849437973472</v>
       </c>
-      <c r="P99" s="5">
+      <c r="P99" s="3">
         <f t="shared" si="5"/>
         <v>5.6744971757433128E-3</v>
       </c>
-      <c r="Q99" s="5">
+      <c r="Q99" s="3">
         <f t="shared" si="6"/>
         <v>3.441837333248798E-3</v>
       </c>
-      <c r="R99" s="5">
+      <c r="R99" s="3">
         <f t="shared" si="7"/>
         <v>9.9981294662833081E-14</v>
       </c>
-      <c r="S99" s="5">
+      <c r="S99" s="3">
         <f t="shared" si="8"/>
         <v>1.7873115264808569E-3</v>
       </c>
@@ -7364,19 +7337,19 @@
       <c r="O100">
         <v>33.840071453395083</v>
       </c>
-      <c r="P100" s="5">
+      <c r="P100" s="3">
         <f t="shared" si="5"/>
         <v>1.422271013906814E-2</v>
       </c>
-      <c r="Q100" s="5">
+      <c r="Q100" s="3">
         <f t="shared" si="6"/>
         <v>9.5116199036734614E-3</v>
       </c>
-      <c r="R100" s="5">
+      <c r="R100" s="3">
         <f t="shared" si="7"/>
         <v>1.0454617909945555E-14</v>
       </c>
-      <c r="S100" s="5">
+      <c r="S100" s="3">
         <f t="shared" si="8"/>
         <v>3.0534422425774425E-3</v>
       </c>
@@ -7427,19 +7400,19 @@
       <c r="O101">
         <v>38.360574615446239</v>
       </c>
-      <c r="P101" s="5">
+      <c r="P101" s="3">
         <f t="shared" si="5"/>
         <v>1.3872030356800619E-2</v>
       </c>
-      <c r="Q101" s="5">
+      <c r="Q101" s="3">
         <f t="shared" si="6"/>
         <v>0.12772103549454805</v>
       </c>
-      <c r="R101" s="5">
+      <c r="R101" s="3">
         <f t="shared" si="7"/>
         <v>2.2391787876065524E-14</v>
       </c>
-      <c r="S101" s="5">
+      <c r="S101" s="3">
         <f t="shared" si="8"/>
         <v>4.0080321608720361E-3</v>
       </c>
@@ -7490,19 +7463,19 @@
       <c r="O102">
         <v>35.389537169374229</v>
       </c>
-      <c r="P102" s="5">
+      <c r="P102" s="3">
         <f t="shared" si="5"/>
         <v>2.4765007138268135E-2</v>
       </c>
-      <c r="Q102" s="5">
+      <c r="Q102" s="3">
         <f t="shared" si="6"/>
         <v>0.14531858042887111</v>
       </c>
-      <c r="R102" s="5">
+      <c r="R102" s="3">
         <f t="shared" si="7"/>
         <v>3.8476266096728288E-14</v>
       </c>
-      <c r="S102" s="5">
+      <c r="S102" s="3">
         <f t="shared" si="8"/>
         <v>3.5273478522917104E-3</v>
       </c>
@@ -7553,19 +7526,19 @@
       <c r="O103">
         <v>35.493053335725662</v>
       </c>
-      <c r="P103" s="5">
+      <c r="P103" s="3">
         <f t="shared" si="5"/>
         <v>1.340311540747992E-2</v>
       </c>
-      <c r="Q103" s="5">
+      <c r="Q103" s="3">
         <f t="shared" si="6"/>
         <v>9.7673419758875953E-3</v>
       </c>
-      <c r="R103" s="5">
+      <c r="R103" s="3">
         <f t="shared" si="7"/>
         <v>8.8495575220318163E-3</v>
       </c>
-      <c r="S103" s="5">
+      <c r="S103" s="3">
         <f t="shared" si="8"/>
         <v>3.538683757499448E-2</v>
       </c>
@@ -7616,19 +7589,19 @@
       <c r="O104">
         <v>36.183779175559202</v>
       </c>
-      <c r="P104" s="5">
+      <c r="P104" s="3">
         <f t="shared" si="5"/>
         <v>4.8668879561151067E-3</v>
       </c>
-      <c r="Q104" s="5">
+      <c r="Q104" s="3">
         <f t="shared" si="6"/>
         <v>8.9606822921773577E-2</v>
       </c>
-      <c r="R104" s="5">
+      <c r="R104" s="3">
         <f t="shared" si="7"/>
         <v>1.2345679012345973E-2</v>
       </c>
-      <c r="S104" s="5">
+      <c r="S104" s="3">
         <f t="shared" si="8"/>
         <v>3.9059968698942203E-2</v>
       </c>
@@ -7679,19 +7652,19 @@
       <c r="O105">
         <v>35.071624469767393</v>
       </c>
-      <c r="P105" s="5">
+      <c r="P105" s="3">
         <f t="shared" si="5"/>
         <v>9.2241022473252415E-3</v>
       </c>
-      <c r="Q105" s="5">
+      <c r="Q105" s="3">
         <f t="shared" si="6"/>
         <v>6.8825816494653844E-2</v>
       </c>
-      <c r="R105" s="5">
+      <c r="R105" s="3">
         <f t="shared" si="7"/>
         <v>1.2856598106870884E-13</v>
       </c>
-      <c r="S105" s="5">
+      <c r="S105" s="3">
         <f t="shared" si="8"/>
         <v>2.621236486851274E-3</v>
       </c>
@@ -7742,19 +7715,19 @@
       <c r="O106">
         <v>34.234116327978633</v>
       </c>
-      <c r="P106" s="5">
+      <c r="P106" s="3">
         <f t="shared" si="5"/>
         <v>4.2682684808011805E-3</v>
       </c>
-      <c r="Q106" s="5">
+      <c r="Q106" s="3">
         <f t="shared" si="6"/>
         <v>1.1709855726363372E-2</v>
       </c>
-      <c r="R106" s="5">
+      <c r="R106" s="3">
         <f t="shared" si="7"/>
         <v>2.9716357122122148E-13</v>
       </c>
-      <c r="S106" s="5">
+      <c r="S106" s="3">
         <f t="shared" si="8"/>
         <v>2.5284490522184122E-3</v>
       </c>
@@ -7805,19 +7778,19 @@
       <c r="O107">
         <v>36.762798408931367</v>
       </c>
-      <c r="P107" s="5">
+      <c r="P107" s="3">
         <f t="shared" si="5"/>
         <v>4.1257705398407632E-3</v>
       </c>
-      <c r="Q107" s="5">
+      <c r="Q107" s="3">
         <f t="shared" si="6"/>
         <v>2.0833951343937583E-2</v>
       </c>
-      <c r="R107" s="5">
+      <c r="R107" s="3">
         <f t="shared" si="7"/>
         <v>1.7787863495637182E-13</v>
       </c>
-      <c r="S107" s="5">
+      <c r="S107" s="3">
         <f t="shared" si="8"/>
         <v>2.9455144982883843E-3</v>
       </c>
@@ -7868,19 +7841,19 @@
       <c r="O108">
         <v>34.716315787362603</v>
       </c>
-      <c r="P108" s="5">
+      <c r="P108" s="3">
         <f t="shared" si="5"/>
         <v>6.5285214689232273E-3</v>
       </c>
-      <c r="Q108" s="5">
+      <c r="Q108" s="3">
         <f t="shared" si="6"/>
         <v>9.9524752748990156E-3</v>
       </c>
-      <c r="R108" s="5">
+      <c r="R108" s="3">
         <f t="shared" si="7"/>
         <v>8.0354157253021212E-14</v>
       </c>
-      <c r="S108" s="5">
+      <c r="S108" s="3">
         <f t="shared" si="8"/>
         <v>1.5163010996649474E-3</v>
       </c>
@@ -7931,19 +7904,19 @@
       <c r="O109">
         <v>36.049732335068747</v>
       </c>
-      <c r="P109" s="5">
+      <c r="P109" s="3">
         <f t="shared" si="5"/>
         <v>5.5940136597184328E-4</v>
       </c>
-      <c r="Q109" s="5">
+      <c r="Q109" s="3">
         <f t="shared" si="6"/>
         <v>0.16706714549947646</v>
       </c>
-      <c r="R109" s="5">
+      <c r="R109" s="3">
         <f t="shared" si="7"/>
         <v>1.0830324909782169E-2</v>
       </c>
-      <c r="S109" s="5">
+      <c r="S109" s="3">
         <f t="shared" si="8"/>
         <v>3.5475762323620479E-2</v>
       </c>
@@ -7994,19 +7967,19 @@
       <c r="O110">
         <v>35.996457635572632</v>
       </c>
-      <c r="P110" s="5">
+      <c r="P110" s="3">
         <f t="shared" si="5"/>
         <v>1.9925292680057879E-2</v>
       </c>
-      <c r="Q110" s="5">
+      <c r="Q110" s="3">
         <f t="shared" si="6"/>
         <v>5.9494918280453675E-2</v>
       </c>
-      <c r="R110" s="5">
+      <c r="R110" s="3">
         <f t="shared" si="7"/>
         <v>1.0752688172042897E-2</v>
       </c>
-      <c r="S110" s="5">
+      <c r="S110" s="3">
         <f t="shared" si="8"/>
         <v>4.10579814622909E-2</v>
       </c>
@@ -8057,19 +8030,19 @@
       <c r="O111">
         <v>36.499629236380912</v>
       </c>
-      <c r="P111" s="5">
+      <c r="P111" s="3">
         <f t="shared" si="5"/>
         <v>5.0946732896833425E-3</v>
       </c>
-      <c r="Q111" s="5">
+      <c r="Q111" s="3">
         <f t="shared" si="6"/>
         <v>7.1345737092787427E-4</v>
       </c>
-      <c r="R111" s="5">
+      <c r="R111" s="3">
         <f t="shared" si="7"/>
         <v>3.5778175310942294E-3</v>
       </c>
-      <c r="S111" s="5">
+      <c r="S111" s="3">
         <f t="shared" si="8"/>
         <v>1.0903707918228195E-2</v>
       </c>
@@ -8120,19 +8093,19 @@
       <c r="O112">
         <v>35.689821358410761</v>
       </c>
-      <c r="P112" s="5">
+      <c r="P112" s="3">
         <f t="shared" si="5"/>
         <v>7.280202099864728E-3</v>
       </c>
-      <c r="Q112" s="5">
+      <c r="Q112" s="3">
         <f t="shared" si="6"/>
         <v>6.2403446103371875E-2</v>
       </c>
-      <c r="R112" s="5">
+      <c r="R112" s="3">
         <f t="shared" si="7"/>
         <v>4.1666666657227463E-3</v>
       </c>
-      <c r="S112" s="5">
+      <c r="S112" s="3">
         <f t="shared" si="8"/>
         <v>1.3850108162090091E-2</v>
       </c>
@@ -8183,19 +8156,19 @@
       <c r="O113">
         <v>33.904891093396657</v>
       </c>
-      <c r="P113" s="5">
+      <c r="P113" s="3">
         <f t="shared" si="5"/>
         <v>1.9386821118152847E-2</v>
       </c>
-      <c r="Q113" s="5">
+      <c r="Q113" s="3">
         <f t="shared" si="6"/>
         <v>0.10860008554161671</v>
       </c>
-      <c r="R113" s="5">
+      <c r="R113" s="3">
         <f t="shared" si="7"/>
         <v>7.0422535211269715E-3</v>
       </c>
-      <c r="S113" s="5">
+      <c r="S113" s="3">
         <f t="shared" si="8"/>
         <v>3.0427456749204749E-2</v>
       </c>
@@ -8246,19 +8219,19 @@
       <c r="O114">
         <v>37.530594818900951</v>
       </c>
-      <c r="P114" s="5">
+      <c r="P114" s="3">
         <f t="shared" si="5"/>
         <v>1.5293419799974067E-2</v>
       </c>
-      <c r="Q114" s="5">
+      <c r="Q114" s="3">
         <f t="shared" si="6"/>
         <v>9.3203333164350616E-2</v>
       </c>
-      <c r="R114" s="5">
+      <c r="R114" s="3">
         <f t="shared" si="7"/>
         <v>1.7442922383248235E-13</v>
       </c>
-      <c r="S114" s="5">
+      <c r="S114" s="3">
         <f t="shared" si="8"/>
         <v>4.3573192020868508E-3</v>
       </c>
@@ -8309,19 +8282,19 @@
       <c r="O115">
         <v>40.967906000376878</v>
       </c>
-      <c r="P115" s="5">
+      <c r="P115" s="3">
         <f t="shared" si="5"/>
         <v>1.3979059002078345E-2</v>
       </c>
-      <c r="Q115" s="5">
+      <c r="Q115" s="3">
         <f t="shared" si="6"/>
         <v>0.17879657344138114</v>
       </c>
-      <c r="R115" s="5">
+      <c r="R115" s="3">
         <f t="shared" si="7"/>
         <v>7.7519379847721713E-3</v>
       </c>
-      <c r="S115" s="5">
+      <c r="S115" s="3">
         <f t="shared" si="8"/>
         <v>2.1000902082178082E-2</v>
       </c>
@@ -8372,19 +8345,19 @@
       <c r="O116">
         <v>38.46570905964662</v>
       </c>
-      <c r="P116" s="5">
+      <c r="P116" s="3">
         <f t="shared" si="5"/>
         <v>1.7316388155094006E-2</v>
       </c>
-      <c r="Q116" s="5">
+      <c r="Q116" s="3">
         <f t="shared" si="6"/>
         <v>0.16604951042491245</v>
       </c>
-      <c r="R116" s="5">
+      <c r="R116" s="3">
         <f t="shared" si="7"/>
         <v>1.0752688171920969E-2</v>
       </c>
-      <c r="S116" s="5">
+      <c r="S116" s="3">
         <f t="shared" si="8"/>
         <v>3.4165315593299002E-2</v>
       </c>
@@ -8435,19 +8408,19 @@
       <c r="O117">
         <v>36.571710804775392</v>
       </c>
-      <c r="P117" s="5">
+      <c r="P117" s="3">
         <f t="shared" si="5"/>
         <v>1.7563001854126973E-4</v>
       </c>
-      <c r="Q117" s="5">
+      <c r="Q117" s="3">
         <f t="shared" si="6"/>
         <v>0.11665030013315192</v>
       </c>
-      <c r="R117" s="5">
+      <c r="R117" s="3">
         <f t="shared" si="7"/>
         <v>7.2463768115611053E-3</v>
       </c>
-      <c r="S117" s="5">
+      <c r="S117" s="3">
         <f t="shared" si="8"/>
         <v>2.1051633313219263E-2</v>
       </c>
@@ -8498,19 +8471,19 @@
       <c r="O118">
         <v>34.672629799738132</v>
       </c>
-      <c r="P118" s="5">
+      <c r="P118" s="3">
         <f t="shared" si="5"/>
         <v>1.2349013090469802E-2</v>
       </c>
-      <c r="Q118" s="5">
+      <c r="Q118" s="3">
         <f t="shared" si="6"/>
         <v>6.9533709667428736E-2</v>
       </c>
-      <c r="R118" s="5">
+      <c r="R118" s="3">
         <f t="shared" si="7"/>
         <v>1.6242270325665743E-13</v>
       </c>
-      <c r="S118" s="5">
+      <c r="S118" s="3">
         <f t="shared" si="8"/>
         <v>3.3389074840988698E-3</v>
       </c>
@@ -8561,19 +8534,19 @@
       <c r="O119">
         <v>34.538483619776898</v>
       </c>
-      <c r="P119" s="5">
+      <c r="P119" s="3">
         <f t="shared" si="5"/>
         <v>4.6326390086599443E-3</v>
       </c>
-      <c r="Q119" s="5">
+      <c r="Q119" s="3">
         <f t="shared" si="6"/>
         <v>1.1343725372687822E-2</v>
       </c>
-      <c r="R119" s="5">
+      <c r="R119" s="3">
         <f t="shared" si="7"/>
         <v>2.7351868810191953E-13</v>
       </c>
-      <c r="S119" s="5">
+      <c r="S119" s="3">
         <f t="shared" si="8"/>
         <v>2.7816465562727423E-3</v>
       </c>
@@ -8624,19 +8597,19 @@
       <c r="O120">
         <v>36.222458200350196</v>
       </c>
-      <c r="P120" s="5">
+      <c r="P120" s="3">
         <f t="shared" si="5"/>
         <v>1.6281189572550571E-2</v>
       </c>
-      <c r="Q120" s="5">
+      <c r="Q120" s="3">
         <f t="shared" si="6"/>
         <v>3.0196227964263082E-3</v>
       </c>
-      <c r="R120" s="5">
+      <c r="R120" s="3">
         <f t="shared" si="7"/>
         <v>1.8852118246754727E-13</v>
       </c>
-      <c r="S120" s="5">
+      <c r="S120" s="3">
         <f t="shared" si="8"/>
         <v>3.1104274414115985E-3</v>
       </c>
@@ -8687,19 +8660,19 @@
       <c r="O121">
         <v>37.527264373111073</v>
       </c>
-      <c r="P121" s="5">
+      <c r="P121" s="3">
         <f t="shared" si="5"/>
         <v>1.6639837063987521E-2</v>
       </c>
-      <c r="Q121" s="5">
+      <c r="Q121" s="3">
         <f t="shared" si="6"/>
         <v>9.4239082330894466E-2</v>
       </c>
-      <c r="R121" s="5">
+      <c r="R121" s="3">
         <f t="shared" si="7"/>
         <v>6.3025210083819429E-3</v>
       </c>
-      <c r="S121" s="5">
+      <c r="S121" s="3">
         <f t="shared" si="8"/>
         <v>1.8891458771196603E-2</v>
       </c>
@@ -8750,19 +8723,19 @@
       <c r="O122">
         <v>36.251959612146507</v>
       </c>
-      <c r="P122" s="5">
+      <c r="P122" s="3">
         <f t="shared" si="5"/>
         <v>1.3493229316515172E-3</v>
       </c>
-      <c r="Q122" s="5">
+      <c r="Q122" s="3">
         <f t="shared" si="6"/>
         <v>4.6737075052670898E-2</v>
       </c>
-      <c r="R122" s="5">
+      <c r="R122" s="3">
         <f t="shared" si="7"/>
         <v>1.6077170416506222E-3</v>
       </c>
-      <c r="S122" s="5">
+      <c r="S122" s="3">
         <f t="shared" si="8"/>
         <v>5.3176652666271128E-3</v>
       </c>
@@ -8813,19 +8786,19 @@
       <c r="O123">
         <v>39.799721673213277</v>
       </c>
-      <c r="P123" s="5">
+      <c r="P123" s="3">
         <f t="shared" si="5"/>
         <v>1.0890772882617472E-2</v>
       </c>
-      <c r="Q123" s="5">
+      <c r="Q123" s="3">
         <f t="shared" si="6"/>
         <v>5.4480592093669941E-2</v>
       </c>
-      <c r="R123" s="5">
+      <c r="R123" s="3">
         <f t="shared" si="7"/>
         <v>4.065040650448634E-3</v>
       </c>
-      <c r="S123" s="5">
+      <c r="S123" s="3">
         <f t="shared" si="8"/>
         <v>1.1731267736319601E-2</v>
       </c>
@@ -8876,19 +8849,19 @@
       <c r="O124">
         <v>34.720404743405823</v>
       </c>
-      <c r="P124" s="5">
+      <c r="P124" s="3">
         <f t="shared" si="5"/>
         <v>4.4421219693225797E-5</v>
       </c>
-      <c r="Q124" s="5">
+      <c r="Q124" s="3">
         <f t="shared" si="6"/>
         <v>1.0283263388230683E-3</v>
       </c>
-      <c r="R124" s="5">
+      <c r="R124" s="3">
         <f t="shared" si="7"/>
         <v>9.4289141514562058E-14</v>
       </c>
-      <c r="S124" s="5">
+      <c r="S124" s="3">
         <f t="shared" si="8"/>
         <v>1.5255539008112748E-3</v>
       </c>
@@ -8939,19 +8912,19 @@
       <c r="O125">
         <v>37.584153779161049</v>
       </c>
-      <c r="P125" s="5">
+      <c r="P125" s="3">
         <f t="shared" si="5"/>
         <v>9.1375030782872839E-4</v>
       </c>
-      <c r="Q125" s="5">
+      <c r="Q125" s="3">
         <f t="shared" si="6"/>
         <v>0.21436757057439898</v>
       </c>
-      <c r="R125" s="5">
+      <c r="R125" s="3">
         <f t="shared" si="7"/>
         <v>8.6580086580183221E-3</v>
       </c>
-      <c r="S125" s="5">
+      <c r="S125" s="3">
         <f t="shared" si="8"/>
         <v>2.346538523689717E-2</v>
       </c>
@@ -9002,19 +8975,19 @@
       <c r="O126">
         <v>35.029716492055123</v>
       </c>
-      <c r="P126" s="5">
+      <c r="P126" s="3">
         <f t="shared" si="5"/>
         <v>1.7675383185548368E-2</v>
       </c>
-      <c r="Q126" s="5">
+      <c r="Q126" s="3">
         <f t="shared" si="6"/>
         <v>7.6961944910508345E-3</v>
       </c>
-      <c r="R126" s="5">
+      <c r="R126" s="3">
         <f t="shared" si="7"/>
         <v>3.3222591362852922E-3</v>
       </c>
-      <c r="S126" s="5">
+      <c r="S126" s="3">
         <f t="shared" si="8"/>
         <v>1.2394215101574398E-2</v>
       </c>
@@ -9065,19 +9038,19 @@
       <c r="O127">
         <v>36.797012077274758</v>
       </c>
-      <c r="P127" s="5">
+      <c r="P127" s="3">
         <f t="shared" si="5"/>
         <v>5.5703678364833094E-3</v>
       </c>
-      <c r="Q127" s="5">
+      <c r="Q127" s="3">
         <f t="shared" si="6"/>
         <v>4.934582890530842E-2</v>
       </c>
-      <c r="R127" s="5">
+      <c r="R127" s="3">
         <f t="shared" si="7"/>
         <v>3.6496350353343041E-3</v>
       </c>
-      <c r="S127" s="5">
+      <c r="S127" s="3">
         <f t="shared" si="8"/>
         <v>1.074676733979898E-2</v>
       </c>
@@ -9128,19 +9101,19 @@
       <c r="O128">
         <v>38.577248423581032</v>
       </c>
-      <c r="P128" s="5">
+      <c r="P128" s="3">
         <f t="shared" si="5"/>
         <v>1.479448286465148E-3</v>
       </c>
-      <c r="Q128" s="5">
+      <c r="Q128" s="3">
         <f t="shared" si="6"/>
         <v>2.5683888309442647E-2</v>
       </c>
-      <c r="R128" s="5">
+      <c r="R128" s="3">
         <f t="shared" si="7"/>
         <v>6.2500000000492864E-3</v>
       </c>
-      <c r="S128" s="5">
+      <c r="S128" s="3">
         <f t="shared" si="8"/>
         <v>2.0171164244037306E-2</v>
       </c>
@@ -9191,19 +9164,19 @@
       <c r="O129">
         <v>39.327756313697911</v>
       </c>
-      <c r="P129" s="5">
+      <c r="P129" s="3">
         <f t="shared" si="5"/>
         <v>2.7743416117959952E-4</v>
       </c>
-      <c r="Q129" s="5">
+      <c r="Q129" s="3">
         <f t="shared" si="6"/>
         <v>2.3442549118069905E-4</v>
       </c>
-      <c r="R129" s="5">
+      <c r="R129" s="3">
         <f t="shared" si="7"/>
         <v>2.6264958579290537E-13</v>
       </c>
-      <c r="S129" s="5">
+      <c r="S129" s="3">
         <f t="shared" si="8"/>
         <v>2.6490112752664643E-3</v>
       </c>
@@ -9254,19 +9227,19 @@
       <c r="O130">
         <v>32.655668546868327</v>
       </c>
-      <c r="P130" s="5">
+      <c r="P130" s="3">
         <f t="shared" si="5"/>
         <v>2.884945995319925E-2</v>
       </c>
-      <c r="Q130" s="5">
+      <c r="Q130" s="3">
         <f t="shared" si="6"/>
         <v>0.14181223484427008</v>
       </c>
-      <c r="R130" s="5">
+      <c r="R130" s="3">
         <f t="shared" si="7"/>
         <v>2.0223539748086294E-13</v>
       </c>
-      <c r="S130" s="5">
+      <c r="S130" s="3">
         <f t="shared" si="8"/>
         <v>2.7063649083492129E-3</v>
       </c>
@@ -9317,19 +9290,19 @@
       <c r="O131">
         <v>35.585444990817606</v>
       </c>
-      <c r="P131" s="5">
+      <c r="P131" s="3">
         <f t="shared" ref="P131:P136" si="9">ABS(H131-L131)/L131</f>
         <v>5.889988369225151E-3</v>
       </c>
-      <c r="Q131" s="5">
+      <c r="Q131" s="3">
         <f t="shared" si="6"/>
         <v>8.2692339824942285E-2</v>
       </c>
-      <c r="R131" s="5">
+      <c r="R131" s="3">
         <f t="shared" si="7"/>
         <v>1.0256410256456312E-2</v>
       </c>
-      <c r="S131" s="5">
+      <c r="S131" s="3">
         <f t="shared" si="8"/>
         <v>3.5809208791955552E-2</v>
       </c>
@@ -9380,19 +9353,19 @@
       <c r="O132">
         <v>36.749910646905683</v>
       </c>
-      <c r="P132" s="5">
+      <c r="P132" s="3">
         <f t="shared" si="9"/>
         <v>7.2778856854040404E-3</v>
       </c>
-      <c r="Q132" s="5">
+      <c r="Q132" s="3">
         <f t="shared" si="6"/>
         <v>2.5969954138635652E-2</v>
       </c>
-      <c r="R132" s="5">
+      <c r="R132" s="3">
         <f t="shared" si="7"/>
         <v>6.9444444443989796E-3</v>
       </c>
-      <c r="S132" s="5">
+      <c r="S132" s="3">
         <f t="shared" si="8"/>
         <v>2.4154981546519062E-2</v>
       </c>
@@ -9443,19 +9416,19 @@
       <c r="O133">
         <v>34.244463577572937</v>
       </c>
-      <c r="P133" s="5">
+      <c r="P133" s="3">
         <f t="shared" si="9"/>
         <v>1.9653625782138372E-2</v>
       </c>
-      <c r="Q133" s="5">
+      <c r="Q133" s="3">
         <f t="shared" si="6"/>
         <v>4.0907565081290863E-2</v>
       </c>
-      <c r="R133" s="5">
+      <c r="R133" s="3">
         <f t="shared" si="7"/>
         <v>2.3714930749456243E-14</v>
       </c>
-      <c r="S133" s="5">
+      <c r="S133" s="3">
         <f t="shared" si="8"/>
         <v>2.4183832259481843E-3</v>
       </c>
@@ -9506,19 +9479,19 @@
       <c r="O134">
         <v>37.446721975213713</v>
       </c>
-      <c r="P134" s="5">
+      <c r="P134" s="3">
         <f t="shared" si="9"/>
         <v>3.4499738702559174E-4</v>
       </c>
-      <c r="Q134" s="5">
+      <c r="Q134" s="3">
         <f t="shared" si="6"/>
         <v>1.2228885395717439E-3</v>
       </c>
-      <c r="R134" s="5">
+      <c r="R134" s="3">
         <f t="shared" si="7"/>
         <v>5.847953216511108E-3</v>
       </c>
-      <c r="S134" s="5">
+      <c r="S134" s="3">
         <f t="shared" si="8"/>
         <v>1.6556171745657423E-2</v>
       </c>
@@ -9569,19 +9542,19 @@
       <c r="O135">
         <v>36.515610209422029</v>
       </c>
-      <c r="P135" s="5">
+      <c r="P135" s="3">
         <f t="shared" si="9"/>
         <v>9.8519293095736815E-3</v>
       </c>
-      <c r="Q135" s="5">
+      <c r="Q135" s="3">
         <f t="shared" si="6"/>
         <v>4.2568911666536827E-2</v>
       </c>
-      <c r="R135" s="5">
+      <c r="R135" s="3">
         <f t="shared" si="7"/>
         <v>2.5925745162468297E-14</v>
       </c>
-      <c r="S135" s="5">
+      <c r="S135" s="3">
         <f t="shared" si="8"/>
         <v>1.8535697122598271E-3</v>
       </c>
@@ -9632,19 +9605,19 @@
       <c r="O136">
         <v>37.424598962393063</v>
       </c>
-      <c r="P136" s="5">
+      <c r="P136" s="3">
         <f t="shared" si="9"/>
         <v>1.8124778645010609E-2</v>
       </c>
-      <c r="Q136" s="5">
+      <c r="Q136" s="3">
         <f t="shared" si="6"/>
         <v>3.3789810108149271E-2</v>
       </c>
-      <c r="R136" s="5">
+      <c r="R136" s="3">
         <f t="shared" si="7"/>
         <v>1.5139066289828326E-16</v>
       </c>
-      <c r="S136" s="5">
+      <c r="S136" s="3">
         <f t="shared" si="8"/>
         <v>2.148230193262532E-3</v>
       </c>

--- a/code/modules/tests/python_regional_new_tort_metrics_merged.xlsx
+++ b/code/modules/tests/python_regional_new_tort_metrics_merged.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/22756463_student_uwa_edu_au/Documents/M4 Backup/dev/octava/code/modules/tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_54D5686D9559133BDB982411595ED87656CC5A09" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{798A1D31-69D1-1D4D-8EEF-5E132D5980AA}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_54D5686D9559133BDB982411595ED87656CC5A09" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8570B77D-F042-0741-881F-0F3437ED0535}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -754,6 +754,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1168,11 +1172,11 @@
         <v>5.1953359436921409E-4</v>
       </c>
       <c r="Q2" s="3">
-        <f t="shared" ref="Q2:S17" si="0">ABS(I2-M2)/M2</f>
+        <f>ABS(I2-M2)/M2</f>
         <v>5.9528128046385721E-2</v>
       </c>
       <c r="R2" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="Q2:S17" si="0">ABS(J2-N2)/N2</f>
         <v>1.5064721596811148E-16</v>
       </c>
       <c r="S2" s="3">
